--- a/CSFA/CSFA Accumilative data.xlsx
+++ b/CSFA/CSFA Accumilative data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://danone.sharepoint.com/sites/AMEA-IndiaCAPEXProjectsTeam/Shared Documents/General/92. Safety Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2896574C-80D7-48FD-862A-210125E1D7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{859435AA-0666-416C-B4BF-41CB164A0478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,17 +21,18 @@
     <sheet name="Sheet5" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CSFA Accumilative data'!$A$1:$S$655</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CSFA Accumilative data'!$A$1:$S$650</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Severity info'!$V$6:$W$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet5!$S$3:$T$19</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="71" r:id="rId7"/>
-    <pivotCache cacheId="72" r:id="rId8"/>
-    <pivotCache cacheId="73" r:id="rId9"/>
-    <pivotCache cacheId="74" r:id="rId10"/>
-    <pivotCache cacheId="75" r:id="rId11"/>
+    <pivotCache cacheId="1136" r:id="rId7"/>
+    <pivotCache cacheId="1137" r:id="rId8"/>
+    <pivotCache cacheId="1138" r:id="rId9"/>
+    <pivotCache cacheId="1139" r:id="rId10"/>
+    <pivotCache cacheId="1140" r:id="rId11"/>
+    <pivotCache cacheId="1141" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4537" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4897" uniqueCount="843">
   <si>
     <t>HIPO</t>
   </si>
@@ -2143,6 +2144,174 @@
     <t>Person observed without googles in the hot work area</t>
   </si>
   <si>
+    <t>scaffolding newly place with base not hard and moving not levelled. further, sariya protruding out of structure when enter in pipeline network</t>
+  </si>
+  <si>
+    <t>Access ladder is not fixed,railing has sharp edges</t>
+  </si>
+  <si>
+    <t>Material is not stored properly.</t>
+  </si>
+  <si>
+    <t>Wall curing work at height without a safety harness.</t>
+  </si>
+  <si>
+    <t>Pls check pit as water drain in it is broken leading to it is just getting filled and no water outlet from there. There is risk that sand area is exposed to water and can affect whole road outside canteen and weak the foundation</t>
+  </si>
+  <si>
+    <t>Person observed standing on stair-case platform without safety harness &amp; Railing</t>
+  </si>
+  <si>
+    <t>Person observed climbing the Scaffolding by outer side of the scaffolding by stepping on scaffolding rungs</t>
+  </si>
+  <si>
+    <t>Person observed standing on Toe guard provided at boom lift platform</t>
+  </si>
+  <si>
+    <t>Debries observed on the beams left creating risk of falling</t>
+  </si>
+  <si>
+    <t>No work is going on due to rain, however housekeeping need to be improved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No worker in the area </t>
+  </si>
+  <si>
+    <t>Walking on i beam channel at 1m height. Risk of fall and injury.</t>
+  </si>
+  <si>
+    <t>Unsafe ladder for movement. Weak railing and width issue of ladder</t>
+  </si>
+  <si>
+    <t>Sharp points to be covered with pads to avoid injury</t>
+  </si>
+  <si>
+    <t>The railing is not linear and horizontal and is it on weak support. To be corrected.</t>
+  </si>
+  <si>
+    <t>The sweeping powder is kept at the entrance of the Oil Inject Blend area. Additionally, shoe covers are not available, and the PPE box and PPE's are missing</t>
+  </si>
+  <si>
+    <t>SPX Flow</t>
+  </si>
+  <si>
+    <t>The TCA gallery area is occupied with stored machines and other materials, causing obstruction and poor housekeeping. . Additionally, an idle conveyor is placed near the entrance, creating a potential safety and accessibility risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCA gallery </t>
+  </si>
+  <si>
+    <t>Confined space activity about to start, gas testing done by vendor, proper access maintained, PTW followed, jsa available at site. Appreciated team</t>
+  </si>
+  <si>
+    <t>Worker sitting on stacked scaffold, potential of material slipping and injury</t>
+  </si>
+  <si>
+    <t>Non standard hammer used at site,non standard wooden planks used for scaffold errection</t>
+  </si>
+  <si>
+    <t>Three points contact not maintained while climbing the chiller building ladder</t>
+  </si>
+  <si>
+    <t>Fall protection is not adequate , forth floor which has opening not blocked</t>
+  </si>
+  <si>
+    <t>Scrap material is not being disposed of in the scrap yard.</t>
+  </si>
+  <si>
+    <t>Sand and aggregate have been stored in the assembly area.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCEPL </t>
+  </si>
+  <si>
+    <t>Material has been lying here for a long time.</t>
+  </si>
+  <si>
+    <t>Gas cylinders are not stored properly.</t>
+  </si>
+  <si>
+    <t>Wooden waste has been dumped in the metal scrap yard.</t>
+  </si>
+  <si>
+    <t>Pls check entry to contractor area where construction of pipe network going on with puds and water loggings potential of slipping. Area is not prepared to absorb water related gaps due to monsoon.</t>
+  </si>
+  <si>
+    <t>During rainy weather electrical distribution board without canopy to protect from rain</t>
+  </si>
+  <si>
+    <t>Only 2 out rigger provided for scaffolding and person working on scaffolding doing drilling work</t>
+  </si>
+  <si>
+    <t>Electric cable tied with metal bar-bending wire at evaporator staircase railing</t>
+  </si>
+  <si>
+    <t>Electrical db with out cover for weather protection at evaporator roof</t>
+  </si>
+  <si>
+    <t>Scaffolding material was found lying in the open at the site.</t>
+  </si>
+  <si>
+    <t>CCEPL (Renucor)</t>
+  </si>
+  <si>
+    <t>Debris bags and other material were found lying at the site. Proper housekeeping was not maintained.</t>
+  </si>
+  <si>
+    <t>Pipes were found stored without barricading and were not properly secured</t>
+  </si>
+  <si>
+    <t>Loose electrical cables are improperly routed over scaffold and pipeline, creating trip and cable damage hazards.</t>
+  </si>
+  <si>
+    <t>Worker used unsafe platform</t>
+  </si>
+  <si>
+    <t>Wet and slippery floor due to rain water</t>
+  </si>
+  <si>
+    <t>Combustible material not covered with fire blanket</t>
+  </si>
+  <si>
+    <t>no standard ladder used for scaffolding</t>
+  </si>
+  <si>
+    <t>The PPE zone entrance barrier on the chimney side has been broken for the last few days. Due to the damaged barrier, personnel can bypass the designated PPE compliance checkpoint and directly enter the project area without wearing the required personal protective equipment (PPE), creating a potential safety risk.</t>
+  </si>
+  <si>
+    <t>General observations -</t>
+  </si>
+  <si>
+    <t>The handrail of the weighbridge is damaged and does not provide adequate support and protection. This condition can lead to slips, trips, falls, or loss of balance for personnel using the area, potentially resulting in a near miss or injury</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Sharp-edged materials are kept at the periphery of the cooling tower area without proper barricading or edge protection. In the event of a slip, trip, or accidental contact, personnel may suffer cuts, lacerations, or other injuries due to exposure to the sharp edges.</t>
+  </si>
+  <si>
+    <t>Waterlogging has been observed in the contractor yard, particularly at the entrance of the containers. As a temporary arrangement, wooden pallets have been placed to provide access to the containers. This arrangement is unstable and unsuitable for regular use, creating a potential safety hazard for personnel.</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Pipes are not stored in the designated area despite many reminders.</t>
+  </si>
+  <si>
+    <t>Manpower access across the excavation is unsafe.</t>
+  </si>
+  <si>
+    <t>Pipes are not properly secured.</t>
+  </si>
+  <si>
+    <t>Worker was not using the boom lift platform. He was sitting on the pipe to do the work. (Pipe rack near MWRS)</t>
+  </si>
+  <si>
+    <t>Temporary platform not fixed with structure</t>
+  </si>
+  <si>
     <t>(All)</t>
   </si>
   <si>
@@ -2338,9 +2507,6 @@
     <t>5S</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>Human Error</t>
   </si>
   <si>
@@ -2360,6 +2526,9 @@
   </si>
   <si>
     <t>Today boiler material was delivered to the site via a 40 ft trailer.  While the trailer was being reversed, Near Gate No 2 vehicle came into contact with the oil injection side wall ( At Corner) . This resulted in minor damage to the plaster and the safety display board located at the corner.</t>
+  </si>
+  <si>
+    <t>Count of Work at Height</t>
   </si>
   <si>
     <t>Hygiene</t>
@@ -3191,7 +3360,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3532,6 +3701,8 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -7784,6 +7955,39 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TECH EHS" refreshedDate="46210.83315486111" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="138" xr:uid="{7616E4CD-4BD8-4D94-BD4F-849ACC1E8A45}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="J21:J159" sheet="Sheet5"/>
+  </cacheSource>
+  <cacheFields count="1">
+    <cacheField name="Work at Height" numFmtId="0">
+      <sharedItems count="14">
+        <s v="Environment"/>
+        <s v="Work at Height"/>
+        <s v="Access &amp; Egress"/>
+        <s v="PTW &amp; Supervision"/>
+        <s v="PPE"/>
+        <s v="Barricading"/>
+        <s v="Material Management"/>
+        <s v="Sharp edges"/>
+        <s v="Electrical"/>
+        <s v="Housekeeping"/>
+        <s v="Lifting Operations"/>
+        <s v="Unsafe Behavior"/>
+        <s v="Fire Safety"/>
+        <s v="Tools &amp; Equipment"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="54">
   <r>
@@ -35478,8 +35682,553 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="138">
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F3DCE442-E984-435C-855B-6A8AED67F209}" name="PivotTable1" cacheId="74" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{14C13F1C-CEBA-4B3B-9AAA-7B0EDA77EDDD}" name="PivotTable2" cacheId="1140" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A39:B58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="19">
+        <item x="10"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item x="16"/>
+        <item x="3"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="17"/>
+        <item x="5"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Trend" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F3DCE442-E984-435C-855B-6A8AED67F209}" name="PivotTable1" cacheId="1139" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A12:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" sortType="descending">
@@ -35632,134 +36381,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{14C13F1C-CEBA-4B3B-9AAA-7B0EDA77EDDD}" name="PivotTable2" cacheId="75" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A39:B58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="19">
-        <item x="10"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item x="16"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="17"/>
-        <item x="5"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Trend" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2689962E-0BAD-4399-BE8A-D638138784ED}" name="PivotTable3" cacheId="73" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2689962E-0BAD-4399-BE8A-D638138784ED}" name="PivotTable3" cacheId="1138" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E26" firstHeaderRow="1" firstDataRow="4" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -36350,7 +36973,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4A08CB2-D72C-4792-BEC0-8C051E369EFD}" name="PivotTable3" cacheId="73" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4A08CB2-D72C-4792-BEC0-8C051E369EFD}" name="PivotTable3" cacheId="1138" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -36882,7 +37505,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C7D59B3-6129-4A24-8D34-951E80F6C49F}" name="PivotTable2" cacheId="71" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C7D59B3-6129-4A24-8D34-951E80F6C49F}" name="PivotTable2" cacheId="1136" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E3:G20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="1">
     <pivotField showAll="0"/>
@@ -36900,7 +37523,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4358371C-45AE-4E60-AA24-08117E4BB894}" name="PivotTable3" cacheId="72" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4358371C-45AE-4E60-AA24-08117E4BB894}" name="PivotTable3" cacheId="1137" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="K5:L22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -36999,6 +37622,98 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{54913E1B-8F7D-4E8F-90FC-DC02ADFE30C7}" name="PivotTable1" cacheId="1141" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="L22:M37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="15">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Work at Height" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B19912B0-6073-4E34-B3A6-F282897747E3}" name="Vend_monthly_obs" displayName="Vend_monthly_obs" ref="U18:X42" totalsRowShown="0">
   <autoFilter ref="U18:X42" xr:uid="{B19912B0-6073-4E34-B3A6-F282897747E3}"/>
@@ -37035,7 +37750,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{32D845F0-5DF6-47B1-AF72-6FF1C5B60A0D}" name="vendorAvgSevScore" displayName="vendorAvgSevScore" ref="K42:L50" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
   <autoFilter ref="K42:L50" xr:uid="{32D845F0-5DF6-47B1-AF72-6FF1C5B60A0D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{47FA4C09-F49E-47FA-8A9A-3E7CE0377EEB}" name="Vendor" dataDxfId="13" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{47FA4C09-F49E-47FA-8A9A-3E7CE0377EEB}" name="Vendor" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{0B339E98-E643-438B-9309-E603269348E0}" name="Avg. Severity Score" dataDxfId="12">
       <calculatedColumnFormula>I19</calculatedColumnFormula>
     </tableColumn>
@@ -37955,14 +38670,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AI693"/>
+  <dimension ref="A1:AI688"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="164" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="110.28515625" style="27" customWidth="1"/>
-    <col min="4" max="8" width="4.85546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" customWidth="1"/>
+    <col min="4" max="9" width="4.85546875" customWidth="1"/>
     <col min="10" max="10" width="6.140625" customWidth="1"/>
     <col min="11" max="11" width="4.85546875" customWidth="1"/>
     <col min="12" max="12" width="6" customWidth="1"/>
@@ -38066,7 +38780,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="44">
-        <f t="shared" ref="J2:J34" si="0">I2*H2</f>
+        <f>I2*H2</f>
         <v>3</v>
       </c>
       <c r="K2" s="46"/>
@@ -38097,7 +38811,7 @@
     </row>
     <row r="3" spans="1:28" customFormat="1">
       <c r="A3" s="43">
-        <f t="shared" ref="A3:A34" si="1">A2+1</f>
+        <f>A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="130" t="s">
@@ -38119,7 +38833,7 @@
         <v>4</v>
       </c>
       <c r="J3" s="44">
-        <f t="shared" si="0"/>
+        <f>I3*H3</f>
         <v>4</v>
       </c>
       <c r="K3" s="51">
@@ -38163,7 +38877,7 @@
     </row>
     <row r="4" spans="1:28" customFormat="1">
       <c r="A4" s="43">
-        <f t="shared" si="1"/>
+        <f>A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="130" t="s">
@@ -38185,7 +38899,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="44">
-        <f t="shared" si="0"/>
+        <f>I4*H4</f>
         <v>3</v>
       </c>
       <c r="K4" s="51"/>
@@ -38222,7 +38936,7 @@
     </row>
     <row r="5" spans="1:28" customFormat="1">
       <c r="A5" s="43">
-        <f t="shared" si="1"/>
+        <f>A4+1</f>
         <v>4</v>
       </c>
       <c r="B5" s="130" t="s">
@@ -38244,7 +38958,7 @@
         <v>4</v>
       </c>
       <c r="J5" s="44">
-        <f t="shared" si="0"/>
+        <f>I5*H5</f>
         <v>4</v>
       </c>
       <c r="K5" s="51">
@@ -38277,7 +38991,7 @@
     </row>
     <row r="6" spans="1:28" customFormat="1">
       <c r="A6" s="43">
-        <f t="shared" si="1"/>
+        <f>A5+1</f>
         <v>5</v>
       </c>
       <c r="B6" s="130" t="s">
@@ -38303,7 +39017,7 @@
         <v>4</v>
       </c>
       <c r="J6" s="44">
-        <f t="shared" si="0"/>
+        <f>I6*H6</f>
         <v>8</v>
       </c>
       <c r="K6" s="51">
@@ -38339,7 +39053,7 @@
     </row>
     <row r="7" spans="1:28" customFormat="1">
       <c r="A7" s="43">
-        <f t="shared" si="1"/>
+        <f>A6+1</f>
         <v>6</v>
       </c>
       <c r="B7" s="130" t="s">
@@ -38361,7 +39075,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="44">
-        <f t="shared" si="0"/>
+        <f>I7*H7</f>
         <v>4</v>
       </c>
       <c r="K7" s="51">
@@ -38397,7 +39111,7 @@
     </row>
     <row r="8" spans="1:28" customFormat="1">
       <c r="A8" s="43">
-        <f t="shared" si="1"/>
+        <f>A7+1</f>
         <v>7</v>
       </c>
       <c r="B8" s="130" t="s">
@@ -38419,7 +39133,7 @@
         <v>4</v>
       </c>
       <c r="J8" s="44">
-        <f t="shared" si="0"/>
+        <f>I8*H8</f>
         <v>4</v>
       </c>
       <c r="K8" s="51">
@@ -38455,7 +39169,7 @@
     </row>
     <row r="9" spans="1:28" customFormat="1">
       <c r="A9" s="43">
-        <f t="shared" si="1"/>
+        <f>A8+1</f>
         <v>8</v>
       </c>
       <c r="B9" s="130" t="s">
@@ -38477,7 +39191,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="44">
-        <f t="shared" si="0"/>
+        <f>I9*H9</f>
         <v>6</v>
       </c>
       <c r="K9" s="51"/>
@@ -38508,7 +39222,7 @@
     </row>
     <row r="10" spans="1:28" customFormat="1">
       <c r="A10" s="43">
-        <f t="shared" si="1"/>
+        <f>A9+1</f>
         <v>9</v>
       </c>
       <c r="B10" s="130" t="s">
@@ -38530,7 +39244,7 @@
         <v>4</v>
       </c>
       <c r="J10" s="44">
-        <f t="shared" si="0"/>
+        <f>I10*H10</f>
         <v>4</v>
       </c>
       <c r="K10" s="51">
@@ -38568,7 +39282,7 @@
     </row>
     <row r="11" spans="1:28" customFormat="1">
       <c r="A11" s="43">
-        <f t="shared" si="1"/>
+        <f>A10+1</f>
         <v>10</v>
       </c>
       <c r="B11" s="130" t="s">
@@ -38590,7 +39304,7 @@
         <v>3</v>
       </c>
       <c r="J11" s="44">
-        <f t="shared" si="0"/>
+        <f>I11*H11</f>
         <v>3</v>
       </c>
       <c r="K11" s="51"/>
@@ -38621,7 +39335,7 @@
     </row>
     <row r="12" spans="1:28" customFormat="1">
       <c r="A12" s="43">
-        <f t="shared" si="1"/>
+        <f>A11+1</f>
         <v>11</v>
       </c>
       <c r="B12" s="130" t="s">
@@ -38643,7 +39357,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="44">
-        <f t="shared" si="0"/>
+        <f>I12*H12</f>
         <v>3</v>
       </c>
       <c r="K12" s="51"/>
@@ -38674,7 +39388,7 @@
     </row>
     <row r="13" spans="1:28" customFormat="1">
       <c r="A13" s="43">
-        <f t="shared" si="1"/>
+        <f>A12+1</f>
         <v>12</v>
       </c>
       <c r="B13" s="130" t="s">
@@ -38700,7 +39414,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="44">
-        <f t="shared" si="0"/>
+        <f>I13*H13</f>
         <v>3</v>
       </c>
       <c r="K13" s="51"/>
@@ -38731,7 +39445,7 @@
     </row>
     <row r="14" spans="1:28" customFormat="1">
       <c r="A14" s="43">
-        <f t="shared" si="1"/>
+        <f>A13+1</f>
         <v>13</v>
       </c>
       <c r="B14" s="130" t="s">
@@ -38753,7 +39467,7 @@
         <v>4</v>
       </c>
       <c r="J14" s="44">
-        <f t="shared" si="0"/>
+        <f>I14*H14</f>
         <v>4</v>
       </c>
       <c r="K14" s="46">
@@ -38793,7 +39507,7 @@
     </row>
     <row r="15" spans="1:28" customFormat="1">
       <c r="A15" s="43">
-        <f t="shared" si="1"/>
+        <f>A14+1</f>
         <v>14</v>
       </c>
       <c r="B15" s="130" t="s">
@@ -38817,7 +39531,7 @@
         <v>3</v>
       </c>
       <c r="J15" s="44">
-        <f t="shared" si="0"/>
+        <f>I15*H15</f>
         <v>3</v>
       </c>
       <c r="K15" s="51"/>
@@ -38852,7 +39566,7 @@
     </row>
     <row r="16" spans="1:28" customFormat="1">
       <c r="A16" s="43">
-        <f t="shared" si="1"/>
+        <f>A15+1</f>
         <v>15</v>
       </c>
       <c r="B16" s="130" t="s">
@@ -38874,7 +39588,7 @@
         <v>3</v>
       </c>
       <c r="J16" s="44">
-        <f t="shared" si="0"/>
+        <f>I16*H16</f>
         <v>3</v>
       </c>
       <c r="K16" s="51"/>
@@ -38909,7 +39623,7 @@
     </row>
     <row r="17" spans="1:23" customFormat="1">
       <c r="A17" s="43">
-        <f t="shared" si="1"/>
+        <f>A16+1</f>
         <v>16</v>
       </c>
       <c r="B17" s="130" t="s">
@@ -38933,7 +39647,7 @@
         <v>3</v>
       </c>
       <c r="J17" s="44">
-        <f t="shared" si="0"/>
+        <f>I17*H17</f>
         <v>3</v>
       </c>
       <c r="K17" s="51"/>
@@ -38968,7 +39682,7 @@
     </row>
     <row r="18" spans="1:23" customFormat="1">
       <c r="A18" s="43">
-        <f t="shared" si="1"/>
+        <f>A17+1</f>
         <v>17</v>
       </c>
       <c r="B18" s="130" t="s">
@@ -38990,7 +39704,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="44">
-        <f t="shared" si="0"/>
+        <f>I18*H18</f>
         <v>2</v>
       </c>
       <c r="K18" s="51"/>
@@ -39021,7 +39735,7 @@
     </row>
     <row r="19" spans="1:23" customFormat="1">
       <c r="A19" s="43">
-        <f t="shared" si="1"/>
+        <f>A18+1</f>
         <v>18</v>
       </c>
       <c r="B19" s="130" t="s">
@@ -39043,7 +39757,7 @@
         <v>3</v>
       </c>
       <c r="J19" s="44">
-        <f t="shared" si="0"/>
+        <f>I19*H19</f>
         <v>3</v>
       </c>
       <c r="K19" s="51"/>
@@ -39077,7 +39791,7 @@
     </row>
     <row r="20" spans="1:23" customFormat="1">
       <c r="A20" s="43">
-        <f t="shared" si="1"/>
+        <f>A19+1</f>
         <v>19</v>
       </c>
       <c r="B20" s="130" t="s">
@@ -39099,7 +39813,7 @@
         <v>4</v>
       </c>
       <c r="J20" s="44">
-        <f t="shared" si="0"/>
+        <f>I20*H20</f>
         <v>4</v>
       </c>
       <c r="K20" s="51">
@@ -39135,7 +39849,7 @@
     </row>
     <row r="21" spans="1:23" customFormat="1">
       <c r="A21" s="43">
-        <f t="shared" si="1"/>
+        <f>A20+1</f>
         <v>20</v>
       </c>
       <c r="B21" s="130" t="s">
@@ -39157,7 +39871,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="44">
-        <f t="shared" si="0"/>
+        <f>I21*H21</f>
         <v>3</v>
       </c>
       <c r="K21" s="51"/>
@@ -39188,7 +39902,7 @@
     </row>
     <row r="22" spans="1:23" customFormat="1">
       <c r="A22" s="43">
-        <f t="shared" si="1"/>
+        <f>A21+1</f>
         <v>21</v>
       </c>
       <c r="B22" s="130" t="s">
@@ -39210,7 +39924,7 @@
         <v>5</v>
       </c>
       <c r="J22" s="44">
-        <f t="shared" si="0"/>
+        <f>I22*H22</f>
         <v>5</v>
       </c>
       <c r="K22" s="51">
@@ -39246,7 +39960,7 @@
     </row>
     <row r="23" spans="1:23" customFormat="1">
       <c r="A23" s="43">
-        <f t="shared" si="1"/>
+        <f>A22+1</f>
         <v>22</v>
       </c>
       <c r="B23" s="130" t="s">
@@ -39270,7 +39984,7 @@
         <v>3</v>
       </c>
       <c r="J23" s="44">
-        <f t="shared" si="0"/>
+        <f>I23*H23</f>
         <v>3</v>
       </c>
       <c r="K23" s="51"/>
@@ -39301,7 +40015,7 @@
     </row>
     <row r="24" spans="1:23" customFormat="1" ht="30">
       <c r="A24" s="43">
-        <f t="shared" si="1"/>
+        <f>A23+1</f>
         <v>23</v>
       </c>
       <c r="B24" s="130" t="s">
@@ -39325,7 +40039,7 @@
         <v>3</v>
       </c>
       <c r="J24" s="44">
-        <f t="shared" si="0"/>
+        <f>I24*H24</f>
         <v>3</v>
       </c>
       <c r="K24" s="51"/>
@@ -39354,7 +40068,7 @@
     </row>
     <row r="25" spans="1:23" customFormat="1">
       <c r="A25" s="43">
-        <f t="shared" si="1"/>
+        <f>A24+1</f>
         <v>24</v>
       </c>
       <c r="B25" s="130" t="s">
@@ -39378,7 +40092,7 @@
         <v>3</v>
       </c>
       <c r="J25" s="44">
-        <f t="shared" si="0"/>
+        <f>I25*H25</f>
         <v>3</v>
       </c>
       <c r="K25" s="51"/>
@@ -39409,7 +40123,7 @@
     </row>
     <row r="26" spans="1:23" customFormat="1">
       <c r="A26" s="43">
-        <f t="shared" si="1"/>
+        <f>A25+1</f>
         <v>25</v>
       </c>
       <c r="B26" s="130" t="s">
@@ -39433,7 +40147,7 @@
         <v>3</v>
       </c>
       <c r="J26" s="44">
-        <f t="shared" si="0"/>
+        <f>I26*H26</f>
         <v>3</v>
       </c>
       <c r="K26" s="51"/>
@@ -39466,7 +40180,7 @@
     </row>
     <row r="27" spans="1:23" customFormat="1">
       <c r="A27" s="43">
-        <f t="shared" si="1"/>
+        <f>A26+1</f>
         <v>26</v>
       </c>
       <c r="B27" s="130" t="s">
@@ -39488,7 +40202,7 @@
         <v>3</v>
       </c>
       <c r="J27" s="44">
-        <f t="shared" si="0"/>
+        <f>I27*H27</f>
         <v>3</v>
       </c>
       <c r="K27" s="51"/>
@@ -39519,7 +40233,7 @@
     </row>
     <row r="28" spans="1:23" customFormat="1">
       <c r="A28" s="43">
-        <f t="shared" si="1"/>
+        <f>A27+1</f>
         <v>27</v>
       </c>
       <c r="B28" s="130" t="s">
@@ -39541,7 +40255,7 @@
         <v>3</v>
       </c>
       <c r="J28" s="44">
-        <f t="shared" si="0"/>
+        <f>I28*H28</f>
         <v>3</v>
       </c>
       <c r="K28" s="51"/>
@@ -39572,7 +40286,7 @@
     </row>
     <row r="29" spans="1:23" customFormat="1">
       <c r="A29" s="43">
-        <f t="shared" si="1"/>
+        <f>A28+1</f>
         <v>28</v>
       </c>
       <c r="B29" s="130" t="s">
@@ -39594,7 +40308,7 @@
         <v>4</v>
       </c>
       <c r="J29" s="44">
-        <f t="shared" si="0"/>
+        <f>I29*H29</f>
         <v>4</v>
       </c>
       <c r="K29" s="51">
@@ -39630,7 +40344,7 @@
     </row>
     <row r="30" spans="1:23" customFormat="1">
       <c r="A30" s="43">
-        <f t="shared" si="1"/>
+        <f>A29+1</f>
         <v>29</v>
       </c>
       <c r="B30" s="130" t="s">
@@ -39652,7 +40366,7 @@
         <v>4</v>
       </c>
       <c r="J30" s="44">
-        <f t="shared" si="0"/>
+        <f>I30*H30</f>
         <v>4</v>
       </c>
       <c r="K30" s="51"/>
@@ -39686,7 +40400,7 @@
     </row>
     <row r="31" spans="1:23" customFormat="1">
       <c r="A31" s="43">
-        <f t="shared" si="1"/>
+        <f>A30+1</f>
         <v>30</v>
       </c>
       <c r="B31" s="130" t="s">
@@ -39708,7 +40422,7 @@
         <v>3</v>
       </c>
       <c r="J31" s="44">
-        <f t="shared" si="0"/>
+        <f>I31*H31</f>
         <v>3</v>
       </c>
       <c r="K31" s="51"/>
@@ -39739,7 +40453,7 @@
     </row>
     <row r="32" spans="1:23" customFormat="1">
       <c r="A32" s="43">
-        <f t="shared" si="1"/>
+        <f>A31+1</f>
         <v>31</v>
       </c>
       <c r="B32" s="130" t="s">
@@ -39761,7 +40475,7 @@
         <v>3</v>
       </c>
       <c r="J32" s="44">
-        <f t="shared" si="0"/>
+        <f>I32*H32</f>
         <v>3</v>
       </c>
       <c r="K32" s="51"/>
@@ -39792,7 +40506,7 @@
     </row>
     <row r="33" spans="1:23" customFormat="1">
       <c r="A33" s="43">
-        <f t="shared" si="1"/>
+        <f>A32+1</f>
         <v>32</v>
       </c>
       <c r="B33" s="130" t="s">
@@ -39816,7 +40530,7 @@
         <v>3</v>
       </c>
       <c r="J33" s="44">
-        <f t="shared" si="0"/>
+        <f>I33*H33</f>
         <v>3</v>
       </c>
       <c r="K33" s="51"/>
@@ -39849,7 +40563,7 @@
     </row>
     <row r="34" spans="1:23" customFormat="1">
       <c r="A34" s="43">
-        <f t="shared" si="1"/>
+        <f>A33+1</f>
         <v>33</v>
       </c>
       <c r="B34" s="130" t="s">
@@ -39871,7 +40585,7 @@
         <v>3</v>
       </c>
       <c r="J34" s="44">
-        <f t="shared" si="0"/>
+        <f>I34*H34</f>
         <v>3</v>
       </c>
       <c r="K34" s="46"/>
@@ -57149,7 +57863,7 @@
         <v>74</v>
       </c>
       <c r="V356" s="38">
-        <f t="shared" ref="V356:V358" si="2">WEEKDAY(S356,2)</f>
+        <f t="shared" ref="V356:V358" si="0">WEEKDAY(S356,2)</f>
         <v>6</v>
       </c>
     </row>
@@ -57209,7 +57923,7 @@
         <v>74</v>
       </c>
       <c r="V357" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -57270,7 +57984,7 @@
         <v>74</v>
       </c>
       <c r="V358" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -68725,7 +69439,7 @@
     </row>
     <row r="584" spans="1:20" customFormat="1">
       <c r="A584" s="43">
-        <f t="shared" ref="A583:A646" si="3">A583+1</f>
+        <f>A583+1</f>
         <v>583</v>
       </c>
       <c r="C584" s="146" t="s">
@@ -68769,7 +69483,7 @@
     </row>
     <row r="585" spans="1:20" customFormat="1">
       <c r="A585" s="43">
-        <f t="shared" si="3"/>
+        <f>A584+1</f>
         <v>584</v>
       </c>
       <c r="C585" s="146" t="s">
@@ -68813,7 +69527,7 @@
     </row>
     <row r="586" spans="1:20" customFormat="1">
       <c r="A586" s="43">
-        <f t="shared" si="3"/>
+        <f>A585+1</f>
         <v>585</v>
       </c>
       <c r="C586" s="146" t="s">
@@ -68857,7 +69571,7 @@
     </row>
     <row r="587" spans="1:20" customFormat="1">
       <c r="A587" s="43">
-        <f t="shared" si="3"/>
+        <f>A586+1</f>
         <v>586</v>
       </c>
       <c r="C587" s="146" t="s">
@@ -68903,7 +69617,7 @@
     </row>
     <row r="588" spans="1:20" customFormat="1">
       <c r="A588" s="43">
-        <f t="shared" si="3"/>
+        <f>A587+1</f>
         <v>587</v>
       </c>
       <c r="C588" s="146" t="s">
@@ -68947,7 +69661,7 @@
     </row>
     <row r="589" spans="1:20" customFormat="1">
       <c r="A589" s="43">
-        <f t="shared" si="3"/>
+        <f>A588+1</f>
         <v>588</v>
       </c>
       <c r="C589" s="146" t="s">
@@ -68991,7 +69705,7 @@
     </row>
     <row r="590" spans="1:20" customFormat="1">
       <c r="A590" s="43">
-        <f t="shared" si="3"/>
+        <f>A589+1</f>
         <v>589</v>
       </c>
       <c r="C590" s="146" t="s">
@@ -69037,7 +69751,7 @@
     </row>
     <row r="591" spans="1:20" customFormat="1">
       <c r="A591" s="43">
-        <f t="shared" si="3"/>
+        <f>A590+1</f>
         <v>590</v>
       </c>
       <c r="C591" s="146" t="s">
@@ -69081,7 +69795,7 @@
     </row>
     <row r="592" spans="1:20" customFormat="1">
       <c r="A592" s="43">
-        <f t="shared" si="3"/>
+        <f>A591+1</f>
         <v>591</v>
       </c>
       <c r="C592" s="146" t="s">
@@ -69125,7 +69839,7 @@
     </row>
     <row r="593" spans="1:19" customFormat="1">
       <c r="A593" s="43">
-        <f t="shared" si="3"/>
+        <f>A592+1</f>
         <v>592</v>
       </c>
       <c r="C593" s="146" t="s">
@@ -69171,415 +69885,2269 @@
     </row>
     <row r="594" spans="1:19" customFormat="1">
       <c r="A594" s="43">
-        <f t="shared" si="3"/>
+        <f>A593+1</f>
         <v>593</v>
       </c>
-      <c r="C594" s="27"/>
-      <c r="S594" s="38"/>
+      <c r="C594" s="146" t="s">
+        <v>696</v>
+      </c>
+      <c r="D594" s="146"/>
+      <c r="E594" s="146"/>
+      <c r="F594" s="146">
+        <v>0</v>
+      </c>
+      <c r="G594" s="146">
+        <v>3</v>
+      </c>
+      <c r="H594" s="146">
+        <v>1</v>
+      </c>
+      <c r="I594" s="146">
+        <v>3</v>
+      </c>
+      <c r="J594" s="146">
+        <v>3</v>
+      </c>
+      <c r="K594" s="146"/>
+      <c r="L594" s="146"/>
+      <c r="M594" s="146"/>
+      <c r="N594" s="146"/>
+      <c r="O594" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="P594" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R594" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S594" s="38">
+        <v>46209</v>
+      </c>
     </row>
     <row r="595" spans="1:19" customFormat="1">
       <c r="A595" s="43">
-        <f t="shared" si="3"/>
+        <f>A594+1</f>
         <v>594</v>
       </c>
-      <c r="C595" s="27"/>
-      <c r="S595" s="38"/>
+      <c r="C595" s="146" t="s">
+        <v>697</v>
+      </c>
+      <c r="D595" s="146"/>
+      <c r="E595" s="146"/>
+      <c r="F595" s="146">
+        <v>13</v>
+      </c>
+      <c r="G595" s="146">
+        <v>3</v>
+      </c>
+      <c r="H595" s="146">
+        <v>1</v>
+      </c>
+      <c r="I595" s="146">
+        <v>4</v>
+      </c>
+      <c r="J595" s="146">
+        <v>4</v>
+      </c>
+      <c r="K595" s="146">
+        <v>1</v>
+      </c>
+      <c r="L595" s="146"/>
+      <c r="M595" s="146">
+        <v>1</v>
+      </c>
+      <c r="N595" s="146"/>
+      <c r="O595" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="P595" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R595" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="S595" s="38">
+        <v>46209</v>
+      </c>
     </row>
     <row r="596" spans="1:19" customFormat="1">
       <c r="A596" s="43">
-        <f t="shared" si="3"/>
+        <f>A595+1</f>
         <v>595</v>
       </c>
-      <c r="C596" s="27"/>
-      <c r="S596" s="38"/>
+      <c r="C596" s="146" t="s">
+        <v>698</v>
+      </c>
+      <c r="D596" s="146"/>
+      <c r="E596" s="146"/>
+      <c r="F596" s="146">
+        <v>0</v>
+      </c>
+      <c r="G596" s="146">
+        <v>0</v>
+      </c>
+      <c r="H596" s="146">
+        <v>1</v>
+      </c>
+      <c r="I596" s="146">
+        <v>3</v>
+      </c>
+      <c r="J596" s="146">
+        <v>3</v>
+      </c>
+      <c r="K596" s="146"/>
+      <c r="L596" s="146"/>
+      <c r="M596" s="146">
+        <v>1</v>
+      </c>
+      <c r="N596" s="146"/>
+      <c r="O596" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="P596" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R596" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S596" s="38">
+        <v>46209</v>
+      </c>
     </row>
     <row r="597" spans="1:19" customFormat="1">
       <c r="A597" s="43">
-        <f t="shared" si="3"/>
+        <f>A596+1</f>
         <v>596</v>
       </c>
-      <c r="C597" s="27"/>
-      <c r="S597" s="38"/>
+      <c r="C597" s="146" t="s">
+        <v>699</v>
+      </c>
+      <c r="D597" s="146"/>
+      <c r="E597" s="146"/>
+      <c r="F597" s="146">
+        <v>0</v>
+      </c>
+      <c r="G597" s="146">
+        <v>1</v>
+      </c>
+      <c r="H597" s="146">
+        <v>1</v>
+      </c>
+      <c r="I597" s="146">
+        <v>4</v>
+      </c>
+      <c r="J597" s="146">
+        <v>4</v>
+      </c>
+      <c r="K597" s="146">
+        <v>1</v>
+      </c>
+      <c r="L597" s="146">
+        <v>1</v>
+      </c>
+      <c r="M597" s="146"/>
+      <c r="N597" s="146">
+        <v>1</v>
+      </c>
+      <c r="O597" s="146" t="s">
+        <v>50</v>
+      </c>
+      <c r="P597" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R597" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S597" s="38">
+        <v>46209</v>
+      </c>
     </row>
     <row r="598" spans="1:19" customFormat="1">
       <c r="A598" s="43">
-        <f t="shared" si="3"/>
+        <f>A597+1</f>
         <v>597</v>
       </c>
-      <c r="C598" s="27"/>
-      <c r="S598" s="38"/>
+      <c r="C598" s="146" t="s">
+        <v>700</v>
+      </c>
+      <c r="D598" s="146"/>
+      <c r="E598" s="146"/>
+      <c r="F598" s="146">
+        <v>0</v>
+      </c>
+      <c r="G598" s="146">
+        <v>0</v>
+      </c>
+      <c r="H598" s="146">
+        <v>1</v>
+      </c>
+      <c r="I598" s="146">
+        <v>3</v>
+      </c>
+      <c r="J598" s="146">
+        <v>3</v>
+      </c>
+      <c r="K598" s="146"/>
+      <c r="L598" s="146"/>
+      <c r="M598" s="146">
+        <v>1</v>
+      </c>
+      <c r="N598" s="146"/>
+      <c r="O598" s="146" t="s">
+        <v>119</v>
+      </c>
+      <c r="P598" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R598" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="S598" s="38">
+        <v>46210</v>
+      </c>
     </row>
     <row r="599" spans="1:19" customFormat="1">
       <c r="A599" s="43">
-        <f t="shared" si="3"/>
+        <f>A598+1</f>
         <v>598</v>
       </c>
-      <c r="C599" s="27"/>
-      <c r="S599" s="38"/>
+      <c r="C599" s="146" t="s">
+        <v>701</v>
+      </c>
+      <c r="D599" s="146"/>
+      <c r="E599" s="146"/>
+      <c r="F599" s="146">
+        <v>6</v>
+      </c>
+      <c r="G599" s="146">
+        <v>4</v>
+      </c>
+      <c r="H599" s="146">
+        <v>1</v>
+      </c>
+      <c r="I599" s="146">
+        <v>4</v>
+      </c>
+      <c r="J599" s="146">
+        <v>4</v>
+      </c>
+      <c r="K599" s="146">
+        <v>1</v>
+      </c>
+      <c r="L599" s="146"/>
+      <c r="M599" s="146"/>
+      <c r="N599" s="146">
+        <v>1</v>
+      </c>
+      <c r="O599" s="146" t="s">
+        <v>50</v>
+      </c>
+      <c r="P599" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R599" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S599" s="38">
+        <v>46210</v>
+      </c>
     </row>
     <row r="600" spans="1:19" customFormat="1">
       <c r="A600" s="43">
-        <f t="shared" si="3"/>
+        <f>A599+1</f>
         <v>599</v>
       </c>
-      <c r="C600" s="27"/>
-      <c r="S600" s="38"/>
+      <c r="C600" s="146" t="s">
+        <v>702</v>
+      </c>
+      <c r="D600" s="146"/>
+      <c r="E600" s="146"/>
+      <c r="F600" s="146">
+        <v>5</v>
+      </c>
+      <c r="G600" s="146">
+        <v>1</v>
+      </c>
+      <c r="H600" s="146">
+        <v>1</v>
+      </c>
+      <c r="I600" s="146">
+        <v>3</v>
+      </c>
+      <c r="J600" s="146">
+        <v>3</v>
+      </c>
+      <c r="K600" s="146"/>
+      <c r="L600" s="146"/>
+      <c r="M600" s="146"/>
+      <c r="N600" s="146">
+        <v>1</v>
+      </c>
+      <c r="O600" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="P600" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R600" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S600" s="38">
+        <v>46210</v>
+      </c>
     </row>
     <row r="601" spans="1:19" customFormat="1">
       <c r="A601" s="43">
-        <f t="shared" si="3"/>
+        <f>A600+1</f>
         <v>600</v>
       </c>
-      <c r="C601" s="27"/>
-      <c r="S601" s="38"/>
+      <c r="C601" s="146" t="s">
+        <v>703</v>
+      </c>
+      <c r="D601" s="146"/>
+      <c r="E601" s="146"/>
+      <c r="F601" s="146">
+        <v>1</v>
+      </c>
+      <c r="G601" s="146">
+        <v>1</v>
+      </c>
+      <c r="H601" s="146">
+        <v>1</v>
+      </c>
+      <c r="I601" s="146">
+        <v>3</v>
+      </c>
+      <c r="J601" s="146">
+        <v>3</v>
+      </c>
+      <c r="K601" s="146"/>
+      <c r="L601" s="146"/>
+      <c r="M601" s="146"/>
+      <c r="N601" s="146">
+        <v>1</v>
+      </c>
+      <c r="O601" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="P601" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R601" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S601" s="38">
+        <v>46210</v>
+      </c>
     </row>
     <row r="602" spans="1:19" customFormat="1">
       <c r="A602" s="43">
-        <f t="shared" si="3"/>
+        <f>A601+1</f>
         <v>601</v>
       </c>
-      <c r="C602" s="27"/>
-      <c r="S602" s="38"/>
+      <c r="C602" s="146" t="s">
+        <v>704</v>
+      </c>
+      <c r="D602" s="146"/>
+      <c r="E602" s="146"/>
+      <c r="F602" s="146">
+        <v>0</v>
+      </c>
+      <c r="G602" s="146">
+        <v>0</v>
+      </c>
+      <c r="H602" s="146">
+        <v>1</v>
+      </c>
+      <c r="I602" s="146">
+        <v>2</v>
+      </c>
+      <c r="J602" s="146">
+        <v>2</v>
+      </c>
+      <c r="K602" s="146"/>
+      <c r="L602" s="146"/>
+      <c r="M602" s="146">
+        <v>1</v>
+      </c>
+      <c r="N602" s="146"/>
+      <c r="O602" s="146" t="s">
+        <v>119</v>
+      </c>
+      <c r="P602" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R602" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="S602" s="38">
+        <v>46209</v>
+      </c>
     </row>
     <row r="603" spans="1:19" customFormat="1">
       <c r="A603" s="43">
-        <f t="shared" si="3"/>
+        <f>A602+1</f>
         <v>602</v>
       </c>
-      <c r="C603" s="27"/>
-      <c r="S603" s="38"/>
+      <c r="C603" s="146" t="s">
+        <v>705</v>
+      </c>
+      <c r="D603" s="146"/>
+      <c r="E603" s="146"/>
+      <c r="F603" s="146">
+        <v>0</v>
+      </c>
+      <c r="G603" s="146">
+        <v>0</v>
+      </c>
+      <c r="H603" s="146">
+        <v>1</v>
+      </c>
+      <c r="I603" s="146">
+        <v>1</v>
+      </c>
+      <c r="J603" s="146">
+        <v>1</v>
+      </c>
+      <c r="K603" s="146"/>
+      <c r="L603" s="146"/>
+      <c r="M603" s="146"/>
+      <c r="N603" s="146"/>
+      <c r="O603" s="146" t="s">
+        <v>706</v>
+      </c>
+      <c r="P603" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R603" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S603" s="38">
+        <v>46210</v>
+      </c>
     </row>
     <row r="604" spans="1:19" customFormat="1">
       <c r="A604" s="43">
-        <f t="shared" si="3"/>
+        <f>A603+1</f>
         <v>603</v>
       </c>
-      <c r="C604" s="27"/>
-      <c r="S604" s="38"/>
+      <c r="C604" s="146" t="s">
+        <v>707</v>
+      </c>
+      <c r="D604" s="146"/>
+      <c r="E604" s="146"/>
+      <c r="F604" s="146">
+        <v>8</v>
+      </c>
+      <c r="G604" s="146">
+        <v>1</v>
+      </c>
+      <c r="H604" s="146">
+        <v>1</v>
+      </c>
+      <c r="I604" s="146">
+        <v>4</v>
+      </c>
+      <c r="J604" s="146">
+        <v>4</v>
+      </c>
+      <c r="K604" s="146">
+        <v>1</v>
+      </c>
+      <c r="L604" s="146"/>
+      <c r="M604" s="146"/>
+      <c r="N604" s="146">
+        <v>1</v>
+      </c>
+      <c r="O604" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="P604" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R604" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="S604" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="605" spans="1:19" customFormat="1">
       <c r="A605" s="43">
-        <f t="shared" si="3"/>
+        <f>A604+1</f>
         <v>604</v>
       </c>
-      <c r="C605" s="27"/>
-      <c r="S605" s="38"/>
+      <c r="C605" s="146" t="s">
+        <v>708</v>
+      </c>
+      <c r="D605" s="146"/>
+      <c r="E605" s="146"/>
+      <c r="F605" s="146">
+        <v>0</v>
+      </c>
+      <c r="G605" s="146">
+        <v>0</v>
+      </c>
+      <c r="H605" s="146">
+        <v>1</v>
+      </c>
+      <c r="I605" s="146">
+        <v>3</v>
+      </c>
+      <c r="J605" s="146">
+        <v>3</v>
+      </c>
+      <c r="K605" s="146"/>
+      <c r="L605" s="146"/>
+      <c r="M605" s="146">
+        <v>1</v>
+      </c>
+      <c r="N605" s="146"/>
+      <c r="O605" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="P605" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R605" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="S605" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="606" spans="1:19" customFormat="1">
       <c r="A606" s="43">
-        <f t="shared" si="3"/>
+        <f>A605+1</f>
         <v>605</v>
       </c>
-      <c r="C606" s="27"/>
-      <c r="S606" s="38"/>
+      <c r="C606" s="146" t="s">
+        <v>709</v>
+      </c>
+      <c r="D606" s="146"/>
+      <c r="E606" s="146"/>
+      <c r="F606" s="146">
+        <v>0</v>
+      </c>
+      <c r="G606" s="146">
+        <v>0</v>
+      </c>
+      <c r="H606" s="146">
+        <v>1</v>
+      </c>
+      <c r="I606" s="146">
+        <v>3</v>
+      </c>
+      <c r="J606" s="146">
+        <v>3</v>
+      </c>
+      <c r="K606" s="146"/>
+      <c r="L606" s="146"/>
+      <c r="M606" s="146">
+        <v>1</v>
+      </c>
+      <c r="N606" s="146"/>
+      <c r="O606" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="P606" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R606" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="S606" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="607" spans="1:19" customFormat="1">
       <c r="A607" s="43">
-        <f t="shared" si="3"/>
+        <f>A606+1</f>
         <v>606</v>
       </c>
-      <c r="C607" s="27"/>
-      <c r="S607" s="38"/>
+      <c r="C607" s="146" t="s">
+        <v>710</v>
+      </c>
+      <c r="D607" s="146"/>
+      <c r="E607" s="146"/>
+      <c r="F607" s="146">
+        <v>0</v>
+      </c>
+      <c r="G607" s="146">
+        <v>0</v>
+      </c>
+      <c r="H607" s="146">
+        <v>1</v>
+      </c>
+      <c r="I607" s="146">
+        <v>1</v>
+      </c>
+      <c r="J607" s="146">
+        <v>1</v>
+      </c>
+      <c r="K607" s="146"/>
+      <c r="L607" s="146"/>
+      <c r="M607" s="146">
+        <v>1</v>
+      </c>
+      <c r="N607" s="146"/>
+      <c r="O607" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="P607" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R607" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="S607" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="608" spans="1:19" customFormat="1">
       <c r="A608" s="43">
-        <f t="shared" si="3"/>
+        <f>A607+1</f>
         <v>607</v>
       </c>
-      <c r="C608" s="27"/>
-      <c r="S608" s="38"/>
+      <c r="C608" s="146" t="s">
+        <v>711</v>
+      </c>
+      <c r="D608" s="146"/>
+      <c r="E608" s="146"/>
+      <c r="F608" s="146">
+        <v>5</v>
+      </c>
+      <c r="G608" s="146">
+        <v>1</v>
+      </c>
+      <c r="H608" s="146">
+        <v>1</v>
+      </c>
+      <c r="I608" s="146">
+        <v>3</v>
+      </c>
+      <c r="J608" s="146">
+        <v>3</v>
+      </c>
+      <c r="K608" s="146"/>
+      <c r="L608" s="146"/>
+      <c r="M608" s="146">
+        <v>1</v>
+      </c>
+      <c r="N608" s="146"/>
+      <c r="O608" s="146" t="s">
+        <v>712</v>
+      </c>
+      <c r="P608" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R608" s="146" t="s">
+        <v>108</v>
+      </c>
+      <c r="S608" s="38">
+        <v>46210</v>
+      </c>
     </row>
     <row r="609" spans="1:19" customFormat="1">
       <c r="A609" s="43">
-        <f t="shared" si="3"/>
+        <f>A608+1</f>
         <v>608</v>
       </c>
-      <c r="C609" s="27"/>
-      <c r="S609" s="38"/>
+      <c r="C609" s="146" t="s">
+        <v>713</v>
+      </c>
+      <c r="D609" s="146"/>
+      <c r="E609" s="146"/>
+      <c r="F609" s="146">
+        <v>0</v>
+      </c>
+      <c r="G609" s="146">
+        <v>0</v>
+      </c>
+      <c r="H609" s="146">
+        <v>1</v>
+      </c>
+      <c r="I609" s="146">
+        <v>3</v>
+      </c>
+      <c r="J609" s="146">
+        <v>3</v>
+      </c>
+      <c r="K609" s="146"/>
+      <c r="L609" s="146"/>
+      <c r="M609" s="146">
+        <v>1</v>
+      </c>
+      <c r="N609" s="146"/>
+      <c r="O609" s="146" t="s">
+        <v>714</v>
+      </c>
+      <c r="P609" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R609" s="146" t="s">
+        <v>108</v>
+      </c>
+      <c r="S609" s="38">
+        <v>46210</v>
+      </c>
     </row>
     <row r="610" spans="1:19" customFormat="1">
       <c r="A610" s="43">
-        <f t="shared" si="3"/>
+        <f>A609+1</f>
         <v>609</v>
       </c>
-      <c r="C610" s="27"/>
-      <c r="S610" s="38"/>
+      <c r="C610" s="146" t="s">
+        <v>715</v>
+      </c>
+      <c r="D610" s="146"/>
+      <c r="E610" s="146"/>
+      <c r="F610" s="146">
+        <v>6</v>
+      </c>
+      <c r="G610" s="146">
+        <v>0</v>
+      </c>
+      <c r="H610" s="146">
+        <v>1</v>
+      </c>
+      <c r="I610" s="146">
+        <v>0</v>
+      </c>
+      <c r="J610" s="146">
+        <v>0</v>
+      </c>
+      <c r="K610" s="146"/>
+      <c r="L610" s="146"/>
+      <c r="M610" s="146"/>
+      <c r="N610" s="146"/>
+      <c r="O610" s="146" t="s">
+        <v>712</v>
+      </c>
+      <c r="P610" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R610" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S610" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="611" spans="1:19" customFormat="1">
       <c r="A611" s="43">
-        <f t="shared" si="3"/>
+        <f>A610+1</f>
         <v>610</v>
       </c>
-      <c r="C611" s="27"/>
-      <c r="S611" s="38"/>
+      <c r="C611" s="146" t="s">
+        <v>716</v>
+      </c>
+      <c r="D611" s="146"/>
+      <c r="E611" s="146"/>
+      <c r="F611" s="146">
+        <v>14</v>
+      </c>
+      <c r="G611" s="146">
+        <v>1</v>
+      </c>
+      <c r="H611" s="146">
+        <v>1</v>
+      </c>
+      <c r="I611" s="146">
+        <v>3</v>
+      </c>
+      <c r="J611" s="146">
+        <v>3</v>
+      </c>
+      <c r="K611" s="146"/>
+      <c r="L611" s="146"/>
+      <c r="M611" s="146"/>
+      <c r="N611" s="146">
+        <v>1</v>
+      </c>
+      <c r="O611" s="146" t="s">
+        <v>50</v>
+      </c>
+      <c r="P611" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R611" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S611" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="612" spans="1:19" customFormat="1">
       <c r="A612" s="43">
-        <f t="shared" si="3"/>
+        <f>A611+1</f>
         <v>611</v>
       </c>
-      <c r="C612" s="27"/>
-      <c r="S612" s="38"/>
+      <c r="C612" s="146" t="s">
+        <v>717</v>
+      </c>
+      <c r="D612" s="146"/>
+      <c r="E612" s="146"/>
+      <c r="F612" s="146">
+        <v>17</v>
+      </c>
+      <c r="G612" s="146">
+        <v>8</v>
+      </c>
+      <c r="H612" s="146">
+        <v>1</v>
+      </c>
+      <c r="I612" s="146">
+        <v>3</v>
+      </c>
+      <c r="J612" s="146">
+        <v>3</v>
+      </c>
+      <c r="K612" s="146"/>
+      <c r="L612" s="146"/>
+      <c r="M612" s="146"/>
+      <c r="N612" s="146">
+        <v>1</v>
+      </c>
+      <c r="O612" s="146" t="s">
+        <v>50</v>
+      </c>
+      <c r="P612" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R612" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S612" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="613" spans="1:19" customFormat="1">
       <c r="A613" s="43">
-        <f t="shared" si="3"/>
+        <f>A612+1</f>
         <v>612</v>
       </c>
-      <c r="C613" s="27"/>
-      <c r="S613" s="38"/>
+      <c r="C613" s="146" t="s">
+        <v>718</v>
+      </c>
+      <c r="D613" s="146"/>
+      <c r="E613" s="146"/>
+      <c r="F613" s="146">
+        <v>8</v>
+      </c>
+      <c r="G613" s="146">
+        <v>3</v>
+      </c>
+      <c r="H613" s="146">
+        <v>1</v>
+      </c>
+      <c r="I613" s="146">
+        <v>5</v>
+      </c>
+      <c r="J613" s="146">
+        <v>5</v>
+      </c>
+      <c r="K613" s="146">
+        <v>1</v>
+      </c>
+      <c r="L613" s="146"/>
+      <c r="M613" s="146"/>
+      <c r="N613" s="146">
+        <v>1</v>
+      </c>
+      <c r="O613" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="P613" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R613" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="S613" s="38">
+        <v>46209</v>
+      </c>
     </row>
     <row r="614" spans="1:19" customFormat="1">
       <c r="A614" s="43">
-        <f t="shared" si="3"/>
+        <f>A613+1</f>
         <v>613</v>
       </c>
-      <c r="C614" s="27"/>
-      <c r="S614" s="38"/>
+      <c r="C614" s="146" t="s">
+        <v>719</v>
+      </c>
+      <c r="D614" s="146"/>
+      <c r="E614" s="146"/>
+      <c r="F614" s="146">
+        <v>0</v>
+      </c>
+      <c r="G614" s="146">
+        <v>2</v>
+      </c>
+      <c r="H614" s="146">
+        <v>1</v>
+      </c>
+      <c r="I614" s="146">
+        <v>5</v>
+      </c>
+      <c r="J614" s="146">
+        <v>5</v>
+      </c>
+      <c r="K614" s="146">
+        <v>1</v>
+      </c>
+      <c r="L614" s="146"/>
+      <c r="M614" s="146"/>
+      <c r="N614" s="146">
+        <v>1</v>
+      </c>
+      <c r="O614" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="P614" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R614" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="S614" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="615" spans="1:19" customFormat="1">
       <c r="A615" s="43">
-        <f t="shared" si="3"/>
+        <f>A614+1</f>
         <v>614</v>
       </c>
-      <c r="C615" s="27"/>
-      <c r="S615" s="38"/>
+      <c r="C615" s="146" t="s">
+        <v>720</v>
+      </c>
+      <c r="D615" s="146"/>
+      <c r="E615" s="146"/>
+      <c r="F615" s="146">
+        <v>0</v>
+      </c>
+      <c r="G615" s="146">
+        <v>0</v>
+      </c>
+      <c r="H615" s="146">
+        <v>1</v>
+      </c>
+      <c r="I615" s="146">
+        <v>2</v>
+      </c>
+      <c r="J615" s="146">
+        <v>2</v>
+      </c>
+      <c r="K615" s="146"/>
+      <c r="L615" s="146"/>
+      <c r="M615" s="146">
+        <v>1</v>
+      </c>
+      <c r="N615" s="146"/>
+      <c r="O615" s="146" t="s">
+        <v>480</v>
+      </c>
+      <c r="P615" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R615" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="S615" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="616" spans="1:19" customFormat="1">
       <c r="A616" s="43">
-        <f t="shared" si="3"/>
+        <f>A615+1</f>
         <v>615</v>
       </c>
-      <c r="C616" s="27"/>
-      <c r="S616" s="38"/>
+      <c r="C616" s="146" t="s">
+        <v>721</v>
+      </c>
+      <c r="D616" s="146"/>
+      <c r="E616" s="146"/>
+      <c r="F616" s="146">
+        <v>0</v>
+      </c>
+      <c r="G616" s="146">
+        <v>0</v>
+      </c>
+      <c r="H616" s="146">
+        <v>1</v>
+      </c>
+      <c r="I616" s="146">
+        <v>3</v>
+      </c>
+      <c r="J616" s="146">
+        <v>3</v>
+      </c>
+      <c r="K616" s="146"/>
+      <c r="L616" s="146"/>
+      <c r="M616" s="146">
+        <v>1</v>
+      </c>
+      <c r="N616" s="146"/>
+      <c r="O616" s="146" t="s">
+        <v>722</v>
+      </c>
+      <c r="P616" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R616" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="S616" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="617" spans="1:19" customFormat="1">
       <c r="A617" s="43">
-        <f t="shared" si="3"/>
+        <f>A616+1</f>
         <v>616</v>
       </c>
-      <c r="C617" s="27"/>
-      <c r="S617" s="38"/>
+      <c r="C617" s="146" t="s">
+        <v>723</v>
+      </c>
+      <c r="D617" s="146"/>
+      <c r="E617" s="146"/>
+      <c r="F617" s="146">
+        <v>0</v>
+      </c>
+      <c r="G617" s="146">
+        <v>0</v>
+      </c>
+      <c r="H617" s="146">
+        <v>1</v>
+      </c>
+      <c r="I617" s="146">
+        <v>3</v>
+      </c>
+      <c r="J617" s="146">
+        <v>3</v>
+      </c>
+      <c r="K617" s="146"/>
+      <c r="L617" s="146"/>
+      <c r="M617" s="146">
+        <v>1</v>
+      </c>
+      <c r="N617" s="146"/>
+      <c r="O617" s="146" t="s">
+        <v>591</v>
+      </c>
+      <c r="P617" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R617" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="S617" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="618" spans="1:19" customFormat="1">
       <c r="A618" s="43">
-        <f t="shared" si="3"/>
+        <f>A617+1</f>
         <v>617</v>
       </c>
-      <c r="C618" s="27"/>
-      <c r="S618" s="38"/>
+      <c r="C618" s="146" t="s">
+        <v>724</v>
+      </c>
+      <c r="D618" s="146"/>
+      <c r="E618" s="146"/>
+      <c r="F618" s="146">
+        <v>0</v>
+      </c>
+      <c r="G618" s="146">
+        <v>0</v>
+      </c>
+      <c r="H618" s="146">
+        <v>1</v>
+      </c>
+      <c r="I618" s="146">
+        <v>3</v>
+      </c>
+      <c r="J618" s="146">
+        <v>3</v>
+      </c>
+      <c r="K618" s="146"/>
+      <c r="L618" s="146"/>
+      <c r="M618" s="146">
+        <v>1</v>
+      </c>
+      <c r="N618" s="146"/>
+      <c r="O618" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="P618" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R618" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="S618" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="619" spans="1:19" customFormat="1">
       <c r="A619" s="43">
-        <f t="shared" si="3"/>
+        <f>A618+1</f>
         <v>618</v>
       </c>
-      <c r="C619" s="27"/>
-      <c r="S619" s="38"/>
+      <c r="C619" s="146" t="s">
+        <v>725</v>
+      </c>
+      <c r="D619" s="146"/>
+      <c r="E619" s="146"/>
+      <c r="F619" s="146">
+        <v>0</v>
+      </c>
+      <c r="G619" s="146">
+        <v>0</v>
+      </c>
+      <c r="H619" s="146">
+        <v>1</v>
+      </c>
+      <c r="I619" s="146">
+        <v>3</v>
+      </c>
+      <c r="J619" s="146">
+        <v>3</v>
+      </c>
+      <c r="K619" s="146"/>
+      <c r="L619" s="146"/>
+      <c r="M619" s="146">
+        <v>1</v>
+      </c>
+      <c r="N619" s="146"/>
+      <c r="O619" s="146" t="s">
+        <v>591</v>
+      </c>
+      <c r="P619" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="R619" s="146" t="s">
+        <v>87</v>
+      </c>
+      <c r="S619" s="38">
+        <v>46211</v>
+      </c>
     </row>
     <row r="620" spans="1:19" customFormat="1">
       <c r="A620" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A620:A650" si="1">A619+1</f>
         <v>619</v>
       </c>
-      <c r="C620" s="27"/>
-      <c r="S620" s="38"/>
+      <c r="C620" s="180" t="s">
+        <v>726</v>
+      </c>
+      <c r="D620" s="181"/>
+      <c r="E620" s="181"/>
+      <c r="F620" s="180">
+        <v>0</v>
+      </c>
+      <c r="G620" s="180">
+        <v>0</v>
+      </c>
+      <c r="H620" s="180">
+        <v>1</v>
+      </c>
+      <c r="I620" s="180">
+        <v>2</v>
+      </c>
+      <c r="J620" s="180">
+        <v>2</v>
+      </c>
+      <c r="K620" s="180"/>
+      <c r="L620" s="180"/>
+      <c r="M620" s="180">
+        <v>1</v>
+      </c>
+      <c r="N620" s="180"/>
+      <c r="O620" s="180" t="s">
+        <v>591</v>
+      </c>
+      <c r="P620" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R620" s="180" t="s">
+        <v>87</v>
+      </c>
+      <c r="S620" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="621" spans="1:19" customFormat="1">
       <c r="A621" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>620</v>
       </c>
-      <c r="C621" s="27"/>
-      <c r="S621" s="38"/>
+      <c r="C621" s="180" t="s">
+        <v>727</v>
+      </c>
+      <c r="D621" s="181"/>
+      <c r="E621" s="181"/>
+      <c r="F621" s="180">
+        <v>0</v>
+      </c>
+      <c r="G621" s="180">
+        <v>0</v>
+      </c>
+      <c r="H621" s="180">
+        <v>1</v>
+      </c>
+      <c r="I621" s="180">
+        <v>4</v>
+      </c>
+      <c r="J621" s="180">
+        <v>4</v>
+      </c>
+      <c r="K621" s="180">
+        <v>1</v>
+      </c>
+      <c r="L621" s="180"/>
+      <c r="M621" s="180">
+        <v>1</v>
+      </c>
+      <c r="N621" s="180"/>
+      <c r="O621" s="180" t="s">
+        <v>480</v>
+      </c>
+      <c r="P621" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R621" s="180" t="s">
+        <v>110</v>
+      </c>
+      <c r="S621" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="622" spans="1:19" customFormat="1">
       <c r="A622" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>621</v>
       </c>
-      <c r="C622" s="27"/>
-      <c r="S622" s="38"/>
+      <c r="C622" s="180" t="s">
+        <v>728</v>
+      </c>
+      <c r="D622" s="181"/>
+      <c r="E622" s="181"/>
+      <c r="F622" s="180">
+        <v>14</v>
+      </c>
+      <c r="G622" s="180">
+        <v>2</v>
+      </c>
+      <c r="H622" s="180">
+        <v>1</v>
+      </c>
+      <c r="I622" s="180">
+        <v>4</v>
+      </c>
+      <c r="J622" s="180">
+        <v>4</v>
+      </c>
+      <c r="K622" s="180">
+        <v>1</v>
+      </c>
+      <c r="L622" s="180"/>
+      <c r="M622" s="180"/>
+      <c r="N622" s="180">
+        <v>1</v>
+      </c>
+      <c r="O622" s="180" t="s">
+        <v>135</v>
+      </c>
+      <c r="P622" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R622" s="180" t="s">
+        <v>110</v>
+      </c>
+      <c r="S622" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="623" spans="1:19" customFormat="1">
       <c r="A623" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>622</v>
       </c>
-      <c r="C623" s="27"/>
-      <c r="S623" s="38"/>
+      <c r="C623" s="180" t="s">
+        <v>729</v>
+      </c>
+      <c r="D623" s="181"/>
+      <c r="E623" s="181"/>
+      <c r="F623" s="180">
+        <v>0</v>
+      </c>
+      <c r="G623" s="180">
+        <v>0</v>
+      </c>
+      <c r="H623" s="180">
+        <v>1</v>
+      </c>
+      <c r="I623" s="180">
+        <v>4</v>
+      </c>
+      <c r="J623" s="180">
+        <v>4</v>
+      </c>
+      <c r="K623" s="180">
+        <v>1</v>
+      </c>
+      <c r="L623" s="180"/>
+      <c r="M623" s="180">
+        <v>1</v>
+      </c>
+      <c r="N623" s="180"/>
+      <c r="O623" s="180" t="s">
+        <v>480</v>
+      </c>
+      <c r="P623" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R623" s="180" t="s">
+        <v>110</v>
+      </c>
+      <c r="S623" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="624" spans="1:19" customFormat="1">
       <c r="A624" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>623</v>
       </c>
-      <c r="C624" s="27"/>
-      <c r="S624" s="38"/>
+      <c r="C624" s="180" t="s">
+        <v>730</v>
+      </c>
+      <c r="D624" s="181"/>
+      <c r="E624" s="181"/>
+      <c r="F624" s="180">
+        <v>0</v>
+      </c>
+      <c r="G624" s="180">
+        <v>0</v>
+      </c>
+      <c r="H624" s="180">
+        <v>1</v>
+      </c>
+      <c r="I624" s="180">
+        <v>3</v>
+      </c>
+      <c r="J624" s="180">
+        <v>3</v>
+      </c>
+      <c r="K624" s="180"/>
+      <c r="L624" s="180"/>
+      <c r="M624" s="180">
+        <v>1</v>
+      </c>
+      <c r="N624" s="180"/>
+      <c r="O624" s="180" t="s">
+        <v>480</v>
+      </c>
+      <c r="P624" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R624" s="180" t="s">
+        <v>110</v>
+      </c>
+      <c r="S624" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="625" spans="1:19" customFormat="1">
       <c r="A625" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>624</v>
       </c>
-      <c r="C625" s="27"/>
-      <c r="S625" s="38"/>
+      <c r="C625" s="180" t="s">
+        <v>731</v>
+      </c>
+      <c r="D625" s="181"/>
+      <c r="E625" s="181"/>
+      <c r="F625" s="180">
+        <v>0</v>
+      </c>
+      <c r="G625" s="180">
+        <v>0</v>
+      </c>
+      <c r="H625" s="180">
+        <v>1</v>
+      </c>
+      <c r="I625" s="180">
+        <v>2</v>
+      </c>
+      <c r="J625" s="180">
+        <v>2</v>
+      </c>
+      <c r="K625" s="180"/>
+      <c r="L625" s="180"/>
+      <c r="M625" s="180">
+        <v>1</v>
+      </c>
+      <c r="N625" s="180"/>
+      <c r="O625" s="180" t="s">
+        <v>732</v>
+      </c>
+      <c r="P625" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R625" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="S625" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="626" spans="1:19" customFormat="1">
       <c r="A626" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>625</v>
       </c>
-      <c r="C626" s="27"/>
-      <c r="S626" s="38"/>
+      <c r="C626" s="180" t="s">
+        <v>733</v>
+      </c>
+      <c r="D626" s="181"/>
+      <c r="E626" s="181"/>
+      <c r="F626" s="180">
+        <v>0</v>
+      </c>
+      <c r="G626" s="180">
+        <v>0</v>
+      </c>
+      <c r="H626" s="180">
+        <v>1</v>
+      </c>
+      <c r="I626" s="180">
+        <v>3</v>
+      </c>
+      <c r="J626" s="180">
+        <v>3</v>
+      </c>
+      <c r="K626" s="180"/>
+      <c r="L626" s="180"/>
+      <c r="M626" s="180">
+        <v>1</v>
+      </c>
+      <c r="N626" s="180"/>
+      <c r="O626" s="180" t="s">
+        <v>732</v>
+      </c>
+      <c r="P626" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R626" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="S626" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="627" spans="1:19" customFormat="1">
       <c r="A627" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>626</v>
       </c>
-      <c r="C627" s="27"/>
-      <c r="S627" s="38"/>
+      <c r="C627" s="180" t="s">
+        <v>734</v>
+      </c>
+      <c r="D627" s="181"/>
+      <c r="E627" s="181"/>
+      <c r="F627" s="180">
+        <v>0</v>
+      </c>
+      <c r="G627" s="180">
+        <v>0</v>
+      </c>
+      <c r="H627" s="180">
+        <v>1</v>
+      </c>
+      <c r="I627" s="180">
+        <v>3</v>
+      </c>
+      <c r="J627" s="180">
+        <v>3</v>
+      </c>
+      <c r="K627" s="180"/>
+      <c r="L627" s="180"/>
+      <c r="M627" s="180">
+        <v>1</v>
+      </c>
+      <c r="N627" s="180"/>
+      <c r="O627" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P627" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R627" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="S627" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="628" spans="1:19" customFormat="1">
       <c r="A628" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>627</v>
       </c>
-      <c r="C628" s="27"/>
-      <c r="S628" s="38"/>
+      <c r="C628" s="180" t="s">
+        <v>731</v>
+      </c>
+      <c r="D628" s="181"/>
+      <c r="E628" s="181"/>
+      <c r="F628" s="180">
+        <v>0</v>
+      </c>
+      <c r="G628" s="180">
+        <v>0</v>
+      </c>
+      <c r="H628" s="180">
+        <v>1</v>
+      </c>
+      <c r="I628" s="180">
+        <v>2</v>
+      </c>
+      <c r="J628" s="180">
+        <v>2</v>
+      </c>
+      <c r="K628" s="180"/>
+      <c r="L628" s="180"/>
+      <c r="M628" s="180">
+        <v>1</v>
+      </c>
+      <c r="N628" s="180"/>
+      <c r="O628" s="180" t="s">
+        <v>732</v>
+      </c>
+      <c r="P628" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R628" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="S628" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="629" spans="1:19" customFormat="1">
       <c r="A629" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>628</v>
       </c>
-      <c r="C629" s="27"/>
-      <c r="S629" s="38"/>
+      <c r="C629" s="180" t="s">
+        <v>733</v>
+      </c>
+      <c r="D629" s="181"/>
+      <c r="E629" s="181"/>
+      <c r="F629" s="180">
+        <v>0</v>
+      </c>
+      <c r="G629" s="180">
+        <v>0</v>
+      </c>
+      <c r="H629" s="180">
+        <v>1</v>
+      </c>
+      <c r="I629" s="180">
+        <v>3</v>
+      </c>
+      <c r="J629" s="180">
+        <v>3</v>
+      </c>
+      <c r="K629" s="180"/>
+      <c r="L629" s="180"/>
+      <c r="M629" s="180">
+        <v>1</v>
+      </c>
+      <c r="N629" s="180"/>
+      <c r="O629" s="180" t="s">
+        <v>732</v>
+      </c>
+      <c r="P629" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R629" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="S629" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="630" spans="1:19" customFormat="1">
       <c r="A630" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>629</v>
       </c>
-      <c r="C630" s="27"/>
-      <c r="S630" s="38"/>
+      <c r="C630" s="180" t="s">
+        <v>734</v>
+      </c>
+      <c r="D630" s="181"/>
+      <c r="E630" s="181"/>
+      <c r="F630" s="180">
+        <v>0</v>
+      </c>
+      <c r="G630" s="180">
+        <v>0</v>
+      </c>
+      <c r="H630" s="180">
+        <v>1</v>
+      </c>
+      <c r="I630" s="180">
+        <v>3</v>
+      </c>
+      <c r="J630" s="180">
+        <v>3</v>
+      </c>
+      <c r="K630" s="180"/>
+      <c r="L630" s="180"/>
+      <c r="M630" s="180">
+        <v>1</v>
+      </c>
+      <c r="N630" s="180"/>
+      <c r="O630" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P630" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R630" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="S630" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="631" spans="1:19" customFormat="1">
       <c r="A631" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>630</v>
       </c>
-      <c r="C631" s="27"/>
-      <c r="S631" s="38"/>
+      <c r="C631" s="180" t="s">
+        <v>735</v>
+      </c>
+      <c r="D631" s="181"/>
+      <c r="E631" s="181"/>
+      <c r="F631" s="180">
+        <v>4</v>
+      </c>
+      <c r="G631" s="180">
+        <v>4</v>
+      </c>
+      <c r="H631" s="180">
+        <v>1</v>
+      </c>
+      <c r="I631" s="180">
+        <v>3</v>
+      </c>
+      <c r="J631" s="180">
+        <v>3</v>
+      </c>
+      <c r="K631" s="180"/>
+      <c r="L631" s="180"/>
+      <c r="M631" s="180">
+        <v>1</v>
+      </c>
+      <c r="N631" s="180"/>
+      <c r="O631" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P631" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R631" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S631" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="632" spans="1:19" customFormat="1">
       <c r="A632" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>631</v>
       </c>
-      <c r="C632" s="27"/>
-      <c r="S632" s="38"/>
+      <c r="C632" s="180" t="s">
+        <v>736</v>
+      </c>
+      <c r="D632" s="180"/>
+      <c r="E632" s="180"/>
+      <c r="F632" s="180">
+        <v>5</v>
+      </c>
+      <c r="G632" s="180">
+        <v>3</v>
+      </c>
+      <c r="H632" s="180">
+        <v>1</v>
+      </c>
+      <c r="I632" s="180">
+        <v>3</v>
+      </c>
+      <c r="J632" s="180">
+        <v>3</v>
+      </c>
+      <c r="K632" s="180"/>
+      <c r="L632" s="180"/>
+      <c r="M632" s="180"/>
+      <c r="N632" s="180">
+        <v>1</v>
+      </c>
+      <c r="O632" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P632" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R632" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S632" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="633" spans="1:19" customFormat="1">
       <c r="A633" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>632</v>
       </c>
-      <c r="C633" s="27"/>
-      <c r="S633" s="38"/>
+      <c r="C633" s="180" t="s">
+        <v>737</v>
+      </c>
+      <c r="D633" s="181"/>
+      <c r="E633" s="180"/>
+      <c r="F633" s="180">
+        <v>0</v>
+      </c>
+      <c r="G633" s="180">
+        <v>0</v>
+      </c>
+      <c r="H633" s="180">
+        <v>1</v>
+      </c>
+      <c r="I633" s="180">
+        <v>2</v>
+      </c>
+      <c r="J633" s="180">
+        <v>2</v>
+      </c>
+      <c r="K633" s="180"/>
+      <c r="L633" s="180"/>
+      <c r="M633" s="180">
+        <v>1</v>
+      </c>
+      <c r="N633" s="180"/>
+      <c r="O633" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P633" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R633" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S633" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="634" spans="1:19" customFormat="1">
       <c r="A634" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>633</v>
       </c>
-      <c r="C634" s="27"/>
-      <c r="S634" s="38"/>
+      <c r="C634" s="180" t="s">
+        <v>738</v>
+      </c>
+      <c r="D634" s="181"/>
+      <c r="E634" s="181"/>
+      <c r="F634" s="180">
+        <v>5</v>
+      </c>
+      <c r="G634" s="180">
+        <v>2</v>
+      </c>
+      <c r="H634" s="180">
+        <v>1</v>
+      </c>
+      <c r="I634" s="180">
+        <v>3</v>
+      </c>
+      <c r="J634" s="180">
+        <v>3</v>
+      </c>
+      <c r="K634" s="180"/>
+      <c r="L634" s="180"/>
+      <c r="M634" s="180"/>
+      <c r="N634" s="180">
+        <v>1</v>
+      </c>
+      <c r="O634" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P634" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R634" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S634" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="635" spans="1:19" customFormat="1">
       <c r="A635" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>634</v>
       </c>
-      <c r="C635" s="27"/>
-      <c r="S635" s="38"/>
+      <c r="C635" s="180" t="s">
+        <v>739</v>
+      </c>
+      <c r="D635" s="181"/>
+      <c r="E635" s="180"/>
+      <c r="F635" s="180">
+        <v>4</v>
+      </c>
+      <c r="G635" s="180">
+        <v>2</v>
+      </c>
+      <c r="H635" s="180">
+        <v>1</v>
+      </c>
+      <c r="I635" s="180">
+        <v>3</v>
+      </c>
+      <c r="J635" s="180">
+        <v>3</v>
+      </c>
+      <c r="K635" s="180"/>
+      <c r="L635" s="180"/>
+      <c r="M635" s="180">
+        <v>1</v>
+      </c>
+      <c r="N635" s="180"/>
+      <c r="O635" s="180" t="s">
+        <v>119</v>
+      </c>
+      <c r="P635" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R635" s="180" t="s">
+        <v>110</v>
+      </c>
+      <c r="S635" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="636" spans="1:19" customFormat="1">
       <c r="A636" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>635</v>
       </c>
-      <c r="C636" s="27"/>
-      <c r="S636" s="38"/>
+      <c r="C636" s="180" t="s">
+        <v>740</v>
+      </c>
+      <c r="D636" s="181"/>
+      <c r="E636" s="181"/>
+      <c r="F636" s="180">
+        <v>1</v>
+      </c>
+      <c r="G636" s="180">
+        <v>10</v>
+      </c>
+      <c r="H636" s="180">
+        <v>1</v>
+      </c>
+      <c r="I636" s="180">
+        <v>4</v>
+      </c>
+      <c r="J636" s="180">
+        <v>4</v>
+      </c>
+      <c r="K636" s="180">
+        <v>1</v>
+      </c>
+      <c r="L636" s="180"/>
+      <c r="M636" s="180">
+        <v>1</v>
+      </c>
+      <c r="N636" s="180"/>
+      <c r="O636" s="180" t="s">
+        <v>741</v>
+      </c>
+      <c r="P636" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R636" s="180" t="s">
+        <v>87</v>
+      </c>
+      <c r="S636" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="637" spans="1:19" customFormat="1">
       <c r="A637" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>636</v>
       </c>
-      <c r="C637" s="27"/>
-      <c r="S637" s="38"/>
+      <c r="C637" s="180" t="s">
+        <v>742</v>
+      </c>
+      <c r="D637" s="181"/>
+      <c r="E637" s="181"/>
+      <c r="F637" s="180">
+        <v>0</v>
+      </c>
+      <c r="G637" s="180">
+        <v>0</v>
+      </c>
+      <c r="H637" s="180">
+        <v>1</v>
+      </c>
+      <c r="I637" s="180">
+        <v>3</v>
+      </c>
+      <c r="J637" s="180">
+        <v>3</v>
+      </c>
+      <c r="K637" s="180"/>
+      <c r="L637" s="180"/>
+      <c r="M637" s="180">
+        <v>1</v>
+      </c>
+      <c r="N637" s="180"/>
+      <c r="O637" s="180" t="s">
+        <v>743</v>
+      </c>
+      <c r="P637" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R637" s="180" t="s">
+        <v>87</v>
+      </c>
+      <c r="S637" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="638" spans="1:19" customFormat="1">
       <c r="A638" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>637</v>
       </c>
-      <c r="C638" s="27"/>
-      <c r="S638" s="38"/>
+      <c r="C638" s="180" t="s">
+        <v>744</v>
+      </c>
+      <c r="D638" s="181"/>
+      <c r="E638" s="181"/>
+      <c r="F638" s="180">
+        <v>0</v>
+      </c>
+      <c r="G638" s="180">
+        <v>0</v>
+      </c>
+      <c r="H638" s="180">
+        <v>1</v>
+      </c>
+      <c r="I638" s="180">
+        <v>3</v>
+      </c>
+      <c r="J638" s="180">
+        <v>3</v>
+      </c>
+      <c r="K638" s="180"/>
+      <c r="L638" s="180"/>
+      <c r="M638" s="180">
+        <v>1</v>
+      </c>
+      <c r="N638" s="180"/>
+      <c r="O638" s="180" t="s">
+        <v>743</v>
+      </c>
+      <c r="P638" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R638" s="180" t="s">
+        <v>87</v>
+      </c>
+      <c r="S638" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="639" spans="1:19" customFormat="1">
       <c r="A639" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>638</v>
       </c>
-      <c r="C639" s="27"/>
-      <c r="S639" s="38"/>
+      <c r="C639" s="180" t="s">
+        <v>745</v>
+      </c>
+      <c r="D639" s="181"/>
+      <c r="E639" s="181"/>
+      <c r="F639" s="180">
+        <v>0</v>
+      </c>
+      <c r="G639" s="180">
+        <v>0</v>
+      </c>
+      <c r="H639" s="180">
+        <v>1</v>
+      </c>
+      <c r="I639" s="180">
+        <v>3</v>
+      </c>
+      <c r="J639" s="180">
+        <v>3</v>
+      </c>
+      <c r="K639" s="180"/>
+      <c r="L639" s="180"/>
+      <c r="M639" s="180">
+        <v>1</v>
+      </c>
+      <c r="N639" s="180"/>
+      <c r="O639" s="180" t="s">
+        <v>746</v>
+      </c>
+      <c r="P639" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R639" s="180" t="s">
+        <v>87</v>
+      </c>
+      <c r="S639" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="640" spans="1:19" customFormat="1">
       <c r="A640" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>639</v>
       </c>
-      <c r="C640" s="27"/>
-      <c r="S640" s="38"/>
+      <c r="C640" s="180" t="s">
+        <v>747</v>
+      </c>
+      <c r="D640" s="181"/>
+      <c r="E640" s="181"/>
+      <c r="F640" s="180">
+        <v>0</v>
+      </c>
+      <c r="G640" s="180">
+        <v>1</v>
+      </c>
+      <c r="H640" s="180">
+        <v>1</v>
+      </c>
+      <c r="I640" s="180">
+        <v>3</v>
+      </c>
+      <c r="J640" s="180">
+        <v>3</v>
+      </c>
+      <c r="K640" s="180"/>
+      <c r="L640" s="180"/>
+      <c r="M640" s="180">
+        <v>1</v>
+      </c>
+      <c r="N640" s="180"/>
+      <c r="O640" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P640" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R640" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S640" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="641" spans="1:19" customFormat="1">
       <c r="A641" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="C641" s="27"/>
-      <c r="S641" s="38"/>
+      <c r="C641" s="180" t="s">
+        <v>748</v>
+      </c>
+      <c r="D641" s="181"/>
+      <c r="E641" s="181"/>
+      <c r="F641" s="180">
+        <v>0</v>
+      </c>
+      <c r="G641" s="180">
+        <v>0</v>
+      </c>
+      <c r="H641" s="180">
+        <v>1</v>
+      </c>
+      <c r="I641" s="180">
+        <v>3</v>
+      </c>
+      <c r="J641" s="180">
+        <v>3</v>
+      </c>
+      <c r="K641" s="180"/>
+      <c r="L641" s="180"/>
+      <c r="M641" s="180">
+        <v>1</v>
+      </c>
+      <c r="N641" s="180"/>
+      <c r="O641" s="180" t="s">
+        <v>50</v>
+      </c>
+      <c r="P641" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R641" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S641" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="642" spans="1:19" customFormat="1">
       <c r="A642" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>641</v>
       </c>
-      <c r="C642" s="27"/>
-      <c r="S642" s="38"/>
+      <c r="C642" s="180" t="s">
+        <v>749</v>
+      </c>
+      <c r="D642" s="180"/>
+      <c r="E642" s="180"/>
+      <c r="F642" s="180">
+        <v>0</v>
+      </c>
+      <c r="G642" s="180">
+        <v>0</v>
+      </c>
+      <c r="H642" s="180">
+        <v>1</v>
+      </c>
+      <c r="I642" s="180">
+        <v>3</v>
+      </c>
+      <c r="J642" s="180">
+        <v>3</v>
+      </c>
+      <c r="K642" s="180"/>
+      <c r="L642" s="180"/>
+      <c r="M642" s="180">
+        <v>1</v>
+      </c>
+      <c r="N642" s="180"/>
+      <c r="O642" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P642" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R642" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S642" s="38">
+        <v>46212</v>
+      </c>
     </row>
     <row r="643" spans="1:19" customFormat="1">
       <c r="A643" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>642</v>
       </c>
-      <c r="C643" s="27"/>
-      <c r="S643" s="38"/>
+      <c r="C643" s="180" t="s">
+        <v>750</v>
+      </c>
+      <c r="D643" s="181"/>
+      <c r="E643" s="181"/>
+      <c r="F643" s="180">
+        <v>1</v>
+      </c>
+      <c r="G643" s="180">
+        <v>1</v>
+      </c>
+      <c r="H643" s="180">
+        <v>1</v>
+      </c>
+      <c r="I643" s="180">
+        <v>4</v>
+      </c>
+      <c r="J643" s="180">
+        <v>4</v>
+      </c>
+      <c r="K643" s="180">
+        <v>1</v>
+      </c>
+      <c r="L643" s="180"/>
+      <c r="M643" s="180">
+        <v>1</v>
+      </c>
+      <c r="N643" s="180"/>
+      <c r="O643" s="180" t="s">
+        <v>67</v>
+      </c>
+      <c r="P643" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R643" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S643" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="644" spans="1:19" customFormat="1">
       <c r="A644" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>643</v>
       </c>
-      <c r="C644" s="27"/>
-      <c r="S644" s="38"/>
+      <c r="C644" s="180" t="s">
+        <v>751</v>
+      </c>
+      <c r="D644" s="181"/>
+      <c r="E644" s="180"/>
+      <c r="F644" s="180">
+        <v>0</v>
+      </c>
+      <c r="G644" s="180">
+        <v>0</v>
+      </c>
+      <c r="H644" s="180">
+        <v>1</v>
+      </c>
+      <c r="I644" s="180">
+        <v>3</v>
+      </c>
+      <c r="J644" s="180">
+        <v>3</v>
+      </c>
+      <c r="K644" s="180"/>
+      <c r="L644" s="180"/>
+      <c r="M644" s="180">
+        <v>1</v>
+      </c>
+      <c r="N644" s="180"/>
+      <c r="O644" s="180" t="s">
+        <v>532</v>
+      </c>
+      <c r="P644" s="180" t="s">
+        <v>74</v>
+      </c>
+      <c r="R644" s="180" t="s">
+        <v>52</v>
+      </c>
+      <c r="S644" s="38">
+        <v>46213</v>
+      </c>
     </row>
     <row r="645" spans="1:19" customFormat="1">
       <c r="A645" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>644</v>
       </c>
       <c r="C645" s="27"/>
@@ -69587,7 +72155,7 @@
     </row>
     <row r="646" spans="1:19" customFormat="1">
       <c r="A646" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>645</v>
       </c>
       <c r="C646" s="27"/>
@@ -69595,7 +72163,7 @@
     </row>
     <row r="647" spans="1:19" customFormat="1">
       <c r="A647" s="43">
-        <f t="shared" ref="A647:A655" si="4">A646+1</f>
+        <f t="shared" si="1"/>
         <v>646</v>
       </c>
       <c r="C647" s="27"/>
@@ -69603,7 +72171,7 @@
     </row>
     <row r="648" spans="1:19" customFormat="1">
       <c r="A648" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>647</v>
       </c>
       <c r="C648" s="27"/>
@@ -69611,7 +72179,7 @@
     </row>
     <row r="649" spans="1:19" customFormat="1">
       <c r="A649" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>648</v>
       </c>
       <c r="C649" s="27"/>
@@ -69619,59 +72187,34 @@
     </row>
     <row r="650" spans="1:19" customFormat="1">
       <c r="A650" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>649</v>
       </c>
       <c r="C650" s="27"/>
       <c r="S650" s="38"/>
     </row>
-    <row r="651" spans="1:19" customFormat="1">
-      <c r="A651" s="43">
-        <f t="shared" si="4"/>
-        <v>650</v>
-      </c>
-      <c r="C651" s="27"/>
-      <c r="S651" s="38"/>
-    </row>
-    <row r="652" spans="1:19" customFormat="1">
-      <c r="A652" s="43">
-        <f t="shared" si="4"/>
-        <v>651</v>
-      </c>
-      <c r="C652" s="27"/>
-      <c r="S652" s="38"/>
-    </row>
-    <row r="653" spans="1:19" customFormat="1">
-      <c r="A653" s="43">
-        <f t="shared" si="4"/>
-        <v>652</v>
-      </c>
-      <c r="C653" s="27"/>
-      <c r="S653" s="38"/>
-    </row>
-    <row r="654" spans="1:19" customFormat="1">
-      <c r="A654" s="43">
-        <f t="shared" si="4"/>
-        <v>653</v>
-      </c>
-      <c r="C654" s="27"/>
-      <c r="S654" s="38"/>
-    </row>
-    <row r="655" spans="1:19" customFormat="1">
-      <c r="A655" s="43">
-        <f t="shared" si="4"/>
-        <v>654</v>
-      </c>
-      <c r="C655" s="27"/>
-      <c r="S655" s="38"/>
+    <row r="651" spans="1:19">
+      <c r="C651" s="17"/>
+      <c r="I651" s="7"/>
+      <c r="J651" s="44"/>
+      <c r="O651" s="7"/>
+      <c r="P651" s="166"/>
+      <c r="R651" s="7"/>
     </row>
     <row r="656" spans="1:19">
-      <c r="C656" s="17"/>
-      <c r="I656" s="7"/>
-      <c r="J656" s="44"/>
-      <c r="O656" s="7"/>
-      <c r="P656" s="166"/>
-      <c r="R656" s="7"/>
+      <c r="R656" s="170"/>
+    </row>
+    <row r="657" spans="18:18">
+      <c r="R657" s="170"/>
+    </row>
+    <row r="658" spans="18:18">
+      <c r="R658" s="170"/>
+    </row>
+    <row r="659" spans="18:18">
+      <c r="R659" s="170"/>
+    </row>
+    <row r="660" spans="18:18">
+      <c r="R660" s="170"/>
     </row>
     <row r="661" spans="18:18">
       <c r="R661" s="170"/>
@@ -69757,26 +72300,11 @@
     <row r="688" spans="18:18">
       <c r="R688" s="170"/>
     </row>
-    <row r="689" spans="18:18">
-      <c r="R689" s="170"/>
-    </row>
-    <row r="690" spans="18:18">
-      <c r="R690" s="170"/>
-    </row>
-    <row r="691" spans="18:18">
-      <c r="R691" s="170"/>
-    </row>
-    <row r="692" spans="18:18">
-      <c r="R692" s="170"/>
-    </row>
-    <row r="693" spans="18:18">
-      <c r="R693" s="170"/>
-    </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:S655" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:S583">
-      <sortCondition ref="S1:S655"/>
+  <autoFilter ref="A1:S650" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S650">
+      <sortCondition ref="S1:S650"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -69819,28 +72347,28 @@
         <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>696</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="28" t="s">
-        <v>697</v>
+        <v>753</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>698</v>
+        <v>754</v>
       </c>
       <c r="S3" s="103"/>
       <c r="T3" s="104"/>
     </row>
     <row r="4" spans="1:20">
       <c r="B4" t="s">
-        <v>699</v>
+        <v>755</v>
       </c>
       <c r="C4" t="s">
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -70020,7 +72548,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="177" t="s">
-        <v>701</v>
+        <v>757</v>
       </c>
       <c r="H16" s="178"/>
       <c r="I16" s="179"/>
@@ -70043,7 +72571,7 @@
       <c r="K17" s="60"/>
       <c r="L17" s="39"/>
       <c r="U17" t="s">
-        <v>702</v>
+        <v>758</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="30">
@@ -70057,46 +72585,46 @@
         <v>3</v>
       </c>
       <c r="G18" s="131" t="s">
-        <v>703</v>
+        <v>759</v>
       </c>
       <c r="H18" s="115"/>
       <c r="I18" s="124" t="s">
-        <v>704</v>
+        <v>760</v>
       </c>
       <c r="J18" s="114" t="s">
-        <v>705</v>
+        <v>761</v>
       </c>
       <c r="K18" s="139" t="s">
-        <v>706</v>
+        <v>762</v>
       </c>
       <c r="L18" s="114" t="s">
         <v>41</v>
       </c>
       <c r="N18" s="114" t="s">
-        <v>703</v>
+        <v>759</v>
       </c>
       <c r="O18" s="114" t="s">
-        <v>707</v>
+        <v>763</v>
       </c>
       <c r="P18" s="137" t="s">
-        <v>708</v>
+        <v>764</v>
       </c>
       <c r="Q18" s="114" t="s">
-        <v>709</v>
+        <v>765</v>
       </c>
       <c r="R18" s="114"/>
       <c r="S18" s="114"/>
       <c r="U18" t="s">
-        <v>710</v>
+        <v>766</v>
       </c>
       <c r="V18" t="s">
         <v>47</v>
       </c>
       <c r="W18" t="s">
-        <v>711</v>
+        <v>767</v>
       </c>
       <c r="X18" t="s">
-        <v>712</v>
+        <v>768</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -70113,10 +72641,10 @@
         <v>28</v>
       </c>
       <c r="G19" s="171" t="s">
-        <v>710</v>
+        <v>766</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="I19" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!O:O,'Severity info'!H19)/COUNTIFS('CSFA Accumilative data'!O:O,'Severity info'!H19)</f>
@@ -70142,7 +72670,7 @@
       </c>
       <c r="P19" s="137">
         <f>COUNTIFS('CSFA Accumilative data'!I:I,'Severity info'!O19)</f>
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="114">
         <f>COUNTIFS('CSFA Accumilative data'!I:I,'Severity info'!O19,'CSFA Accumilative data'!P:P,'Severity info'!N19)</f>
@@ -70180,11 +72708,11 @@
       </c>
       <c r="I20" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!O:O,'Severity info'!H20)/COUNTIFS('CSFA Accumilative data'!O:O,'Severity info'!H20)</f>
-        <v>3.015625</v>
+        <v>3.030075187969925</v>
       </c>
       <c r="J20" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!O:O,'Severity info'!H20)</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K20" s="124">
         <f>SUMIFS('CSFA Accumilative data'!$I$369:$I$553,'CSFA Accumilative data'!$O$369:$O$553,'Severity info'!H20)/COUNTIFS('CSFA Accumilative data'!$O$369:$O$553,'Severity info'!H20)</f>
@@ -70202,7 +72730,7 @@
       </c>
       <c r="P20" s="137">
         <f>COUNTIFS('CSFA Accumilative data'!I:I,'Severity info'!O20)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="114">
         <f>COUNTIFS('CSFA Accumilative data'!I:I,'Severity info'!O20,'CSFA Accumilative data'!P:P,'Severity info'!N20)</f>
@@ -70231,11 +72759,11 @@
       </c>
       <c r="I21" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!O:O,'Severity info'!H21)/COUNTIFS('CSFA Accumilative data'!O:O,'Severity info'!H21)</f>
-        <v>2.9612903225806453</v>
+        <v>2.9763313609467454</v>
       </c>
       <c r="J21" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!O:O,'Severity info'!H21)</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K21" s="124">
         <f>SUMIFS('CSFA Accumilative data'!$I$369:$I$553,'CSFA Accumilative data'!$O$369:$O$553,'Severity info'!H21)/COUNTIFS('CSFA Accumilative data'!$O$369:$O$553,'Severity info'!H21)</f>
@@ -70247,22 +72775,22 @@
       </c>
       <c r="N21" s="114"/>
       <c r="O21" s="114" t="s">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="P21" s="137">
         <f>P19+P20</f>
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="Q21" s="114">
         <f>Q19+Q20</f>
         <v>81</v>
       </c>
       <c r="R21" s="114" t="s">
-        <v>715</v>
+        <v>771</v>
       </c>
       <c r="S21" s="114">
         <f>COUNTA(_xlfn.UNIQUE('CSFA Accumilative data'!S:S))</f>
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U21" t="s">
         <v>50</v>
@@ -70310,14 +72838,14 @@
       <c r="P22" s="137"/>
       <c r="Q22" s="114"/>
       <c r="R22" s="114" t="s">
-        <v>716</v>
+        <v>772</v>
       </c>
       <c r="S22" s="114">
         <f>P21/S21</f>
-        <v>2.2142857142857144</v>
+        <v>2.2127659574468086</v>
       </c>
       <c r="U22" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="V22" t="s">
         <v>53</v>
@@ -70343,7 +72871,7 @@
       </c>
       <c r="I23" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!O:O,'Severity info'!H23)/COUNTIFS('CSFA Accumilative data'!O:O,'Severity info'!H23)</f>
-        <v>2.5692307692307694</v>
+        <v>2.5735294117647061</v>
       </c>
       <c r="J23" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!O:O,'Severity info'!H23)</f>
@@ -70362,11 +72890,11 @@
       <c r="P23" s="137"/>
       <c r="Q23" s="114"/>
       <c r="R23" s="114" t="s">
-        <v>717</v>
+        <v>773</v>
       </c>
       <c r="S23" s="114">
         <f>Q21/P21*100</f>
-        <v>87.096774193548384</v>
+        <v>77.884615384615387</v>
       </c>
       <c r="U23" t="s">
         <v>70</v>
@@ -70410,11 +72938,11 @@
         <v>2</v>
       </c>
       <c r="N24" s="114" t="s">
-        <v>718</v>
+        <v>774</v>
       </c>
       <c r="O24" s="114">
         <f>SUM('CSFA Accumilative data'!N:N)/SUM('CSFA Accumilative data'!M:M)</f>
-        <v>0.49100257069408743</v>
+        <v>0.47764705882352942</v>
       </c>
       <c r="U24" t="s">
         <v>67</v>
@@ -70429,7 +72957,7 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="29" t="s">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -70443,11 +72971,11 @@
       </c>
       <c r="I25" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!O:O,'Severity info'!H25)/COUNTIFS('CSFA Accumilative data'!O:O,'Severity info'!H25)</f>
-        <v>2.8909090909090911</v>
+        <v>2.9523809523809526</v>
       </c>
       <c r="J25" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!O:O,'Severity info'!H25)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K25" s="124">
         <f>SUMIFS('CSFA Accumilative data'!$I$369:$I$553,'CSFA Accumilative data'!$O$369:$O$553,'Severity info'!H25)/COUNTIFS('CSFA Accumilative data'!$O$369:$O$553,'Severity info'!H25)</f>
@@ -70458,11 +72986,11 @@
         <v>10</v>
       </c>
       <c r="N25" t="s">
-        <v>720</v>
+        <v>776</v>
       </c>
       <c r="O25">
         <f>SUM('CSFA Accumilative data'!N:N)</f>
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="U25" t="s">
         <v>135</v>
@@ -70521,18 +73049,18 @@
     </row>
     <row r="27" spans="1:28">
       <c r="G27" s="174" t="s">
-        <v>721</v>
+        <v>777</v>
       </c>
       <c r="H27" s="116" t="s">
         <v>52</v>
       </c>
       <c r="I27" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!R:R,'Severity info'!H27)/COUNTIFS('CSFA Accumilative data'!R:R,'Severity info'!H27)</f>
-        <v>2.9446808510638296</v>
+        <v>2.9450980392156865</v>
       </c>
       <c r="J27" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!R:R,'Severity info'!H27)</f>
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K27" s="124">
         <f>SUMIFS('CSFA Accumilative data'!$I$369:$I$553,'CSFA Accumilative data'!$R$369:$R$553,'Severity info'!H27)/COUNTIFS('CSFA Accumilative data'!$R$369:$R$553,'Severity info'!H27)</f>
@@ -70573,11 +73101,11 @@
       </c>
       <c r="I28" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!R:R,'Severity info'!H28)/COUNTIFS('CSFA Accumilative data'!R:R,'Severity info'!H28)</f>
-        <v>2.78125</v>
+        <v>2.8285714285714287</v>
       </c>
       <c r="J28" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!R:R,'Severity info'!H28)</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K28" s="124">
         <f>SUMIFS('CSFA Accumilative data'!$I$369:$I$553,'CSFA Accumilative data'!$R$369:$R$553,'Severity info'!H28)/COUNTIFS('CSFA Accumilative data'!$R$369:$R$553,'Severity info'!H28)</f>
@@ -70618,7 +73146,7 @@
       </c>
       <c r="I29" s="124">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!R:R,'Severity info'!H29)/COUNTIFS('CSFA Accumilative data'!R:R,'Severity info'!H29)</f>
-        <v>2.676190476190476</v>
+        <v>2.6982758620689653</v>
       </c>
       <c r="J29" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!R:R,'Severity info'!H29)</f>
@@ -70663,7 +73191,7 @@
       </c>
       <c r="I30" s="138">
         <f>SUMIFS('CSFA Accumilative data'!I:I,'CSFA Accumilative data'!R:R,'Severity info'!H30)/COUNTIFS('CSFA Accumilative data'!R:R,'Severity info'!H30)</f>
-        <v>2.5744680851063828</v>
+        <v>2.6</v>
       </c>
       <c r="J30" s="114">
         <f>SUMIFS('CSFA Accumilative data'!N:N,'CSFA Accumilative data'!R:R,'Severity info'!H30)</f>
@@ -70678,7 +73206,7 @@
         <v>9</v>
       </c>
       <c r="U30" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="V30" t="s">
         <v>231</v>
@@ -70692,7 +73220,7 @@
         <v>4</v>
       </c>
       <c r="Z30" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="AA30">
         <v>2</v>
@@ -70785,13 +73313,13 @@
         <v>45</v>
       </c>
       <c r="O34" s="123" t="s">
-        <v>722</v>
+        <v>778</v>
       </c>
       <c r="Q34" s="120" t="s">
-        <v>723</v>
+        <v>779</v>
       </c>
       <c r="R34" s="123" t="s">
-        <v>724</v>
+        <v>780</v>
       </c>
       <c r="U34" t="s">
         <v>82</v>
@@ -70824,14 +73352,14 @@
       </c>
       <c r="O35" s="124">
         <f>I27</f>
-        <v>2.9446808510638296</v>
+        <v>2.9450980392156865</v>
       </c>
       <c r="Q35" s="121" t="s">
-        <v>716</v>
+        <v>772</v>
       </c>
       <c r="R35" s="124">
         <f>S22</f>
-        <v>2.2142857142857144</v>
+        <v>2.2127659574468086</v>
       </c>
       <c r="U35" t="s">
         <v>119</v>
@@ -70855,14 +73383,14 @@
       </c>
       <c r="O36" s="124">
         <f t="shared" ref="O36:O38" si="1">I28</f>
-        <v>2.78125</v>
+        <v>2.8285714285714287</v>
       </c>
       <c r="Q36" s="121" t="s">
-        <v>717</v>
+        <v>773</v>
       </c>
       <c r="R36" s="124">
         <f>S23</f>
-        <v>87.096774193548384</v>
+        <v>77.884615384615387</v>
       </c>
       <c r="U36" t="s">
         <v>103</v>
@@ -70886,14 +73414,14 @@
       </c>
       <c r="O37" s="124">
         <f t="shared" si="1"/>
-        <v>2.676190476190476</v>
+        <v>2.6982758620689653</v>
       </c>
       <c r="Q37" s="121" t="s">
-        <v>718</v>
+        <v>774</v>
       </c>
       <c r="R37" s="124">
         <f>O24</f>
-        <v>0.49100257069408743</v>
+        <v>0.47764705882352942</v>
       </c>
       <c r="U37" t="s">
         <v>50</v>
@@ -70916,17 +73444,17 @@
       </c>
       <c r="O38" s="125">
         <f t="shared" si="1"/>
-        <v>2.5744680851063828</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" s="121" t="s">
-        <v>725</v>
+        <v>781</v>
       </c>
       <c r="R38" s="124">
         <f>P21</f>
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="U38" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="V38" t="s">
         <v>652</v>
@@ -70942,7 +73470,7 @@
     </row>
     <row r="39" spans="1:28">
       <c r="Q39" s="121" t="s">
-        <v>726</v>
+        <v>782</v>
       </c>
       <c r="R39" s="124">
         <v>13</v>
@@ -70964,15 +73492,15 @@
     </row>
     <row r="40" spans="1:28">
       <c r="H40" s="176" t="s">
-        <v>727</v>
+        <v>783</v>
       </c>
       <c r="I40" s="176"/>
       <c r="K40" s="176" t="s">
-        <v>728</v>
+        <v>784</v>
       </c>
       <c r="L40" s="176"/>
       <c r="Q40" s="122" t="s">
-        <v>729</v>
+        <v>785</v>
       </c>
       <c r="R40" s="125"/>
       <c r="U40" t="s">
@@ -71008,16 +73536,16 @@
     </row>
     <row r="42" spans="1:28">
       <c r="H42" s="120" t="s">
-        <v>730</v>
+        <v>786</v>
       </c>
       <c r="I42" s="123" t="s">
-        <v>731</v>
+        <v>787</v>
       </c>
       <c r="K42" s="120" t="s">
-        <v>710</v>
+        <v>766</v>
       </c>
       <c r="L42" s="123" t="s">
-        <v>722</v>
+        <v>778</v>
       </c>
       <c r="U42" t="s">
         <v>82</v>
@@ -71044,7 +73572,7 @@
         <v>95</v>
       </c>
       <c r="K43" s="126" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="L43" s="124">
         <f t="shared" ref="L43:L50" si="2">I19</f>
@@ -71065,7 +73593,7 @@
       </c>
       <c r="L44" s="124">
         <f t="shared" si="2"/>
-        <v>3.015625</v>
+        <v>3.030075187969925</v>
       </c>
       <c r="O44" s="140"/>
     </row>
@@ -71083,7 +73611,7 @@
       </c>
       <c r="L45" s="124">
         <f t="shared" si="2"/>
-        <v>2.9612903225806453</v>
+        <v>2.9763313609467454</v>
       </c>
       <c r="O45" s="140"/>
     </row>
@@ -71119,7 +73647,7 @@
       </c>
       <c r="L47" s="124">
         <f t="shared" si="2"/>
-        <v>2.5692307692307694</v>
+        <v>2.5735294117647061</v>
       </c>
       <c r="O47" s="140"/>
     </row>
@@ -71138,7 +73666,7 @@
       </c>
       <c r="L49" s="124">
         <f t="shared" si="2"/>
-        <v>2.8909090909090911</v>
+        <v>2.9523809523809526</v>
       </c>
     </row>
     <row r="50" spans="11:14">
@@ -71152,10 +73680,10 @@
     </row>
     <row r="54" spans="11:14">
       <c r="L54" s="171" t="s">
-        <v>710</v>
+        <v>766</v>
       </c>
       <c r="M54" s="115" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="N54" s="124">
         <v>2.3333333333333335</v>
@@ -71274,7 +73802,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>732</v>
+        <v>788</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -71335,12 +73863,12 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>732</v>
+        <v>788</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>733</v>
+        <v>789</v>
       </c>
       <c r="C29">
         <v>33</v>
@@ -71348,7 +73876,7 @@
     </row>
     <row r="30" spans="2:3">
       <c r="B30" t="s">
-        <v>734</v>
+        <v>790</v>
       </c>
       <c r="C30">
         <v>12</v>
@@ -71356,7 +73884,7 @@
     </row>
     <row r="31" spans="2:3">
       <c r="B31" t="s">
-        <v>735</v>
+        <v>791</v>
       </c>
       <c r="C31">
         <v>25</v>
@@ -71364,7 +73892,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>736</v>
+        <v>792</v>
       </c>
       <c r="C32">
         <v>18</v>
@@ -71372,7 +73900,7 @@
     </row>
     <row r="33" spans="2:3">
       <c r="B33" t="s">
-        <v>737</v>
+        <v>793</v>
       </c>
       <c r="C33">
         <v>16</v>
@@ -71380,7 +73908,7 @@
     </row>
     <row r="34" spans="2:3">
       <c r="B34" t="s">
-        <v>738</v>
+        <v>794</v>
       </c>
       <c r="C34">
         <v>13</v>
@@ -71388,7 +73916,7 @@
     </row>
     <row r="35" spans="2:3">
       <c r="B35" t="s">
-        <v>739</v>
+        <v>795</v>
       </c>
       <c r="C35">
         <v>18</v>
@@ -71396,7 +73924,7 @@
     </row>
     <row r="36" spans="2:3">
       <c r="B36" t="s">
-        <v>740</v>
+        <v>796</v>
       </c>
       <c r="C36">
         <v>21</v>
@@ -71404,7 +73932,7 @@
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>741</v>
+        <v>797</v>
       </c>
       <c r="C37">
         <v>23</v>
@@ -71412,7 +73940,7 @@
     </row>
     <row r="38" spans="2:3">
       <c r="B38" t="s">
-        <v>742</v>
+        <v>798</v>
       </c>
       <c r="C38">
         <v>28</v>
@@ -71420,7 +73948,7 @@
     </row>
     <row r="39" spans="2:3">
       <c r="B39" t="s">
-        <v>743</v>
+        <v>799</v>
       </c>
       <c r="C39">
         <v>27</v>
@@ -71428,7 +73956,7 @@
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>744</v>
+        <v>800</v>
       </c>
       <c r="C40">
         <v>10</v>
@@ -71469,12 +73997,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="26.25">
       <c r="A2" s="66" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="26.25">
       <c r="A3" s="66" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="E3" s="93"/>
       <c r="F3" s="94"/>
@@ -71485,24 +74013,24 @@
     </row>
     <row r="4" spans="1:15" ht="27" thickBot="1">
       <c r="A4" s="66" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="E4" s="96"/>
       <c r="F4" s="97"/>
       <c r="G4" s="98"/>
       <c r="I4" s="66" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="26.25">
       <c r="A5" s="66" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="E5" s="96"/>
       <c r="F5" s="97"/>
       <c r="G5" s="98"/>
       <c r="I5" s="66" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="K5" s="28" t="s">
         <v>28</v>
@@ -71519,22 +74047,22 @@
     </row>
     <row r="6" spans="1:15" ht="26.25">
       <c r="A6" s="66" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="E6" s="96"/>
       <c r="F6" s="97"/>
       <c r="G6" s="98"/>
       <c r="I6" s="66" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="O6">
         <v>13</v>
@@ -71542,22 +74070,22 @@
     </row>
     <row r="7" spans="1:15" ht="26.25">
       <c r="A7" s="66" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="E7" s="96"/>
       <c r="F7" s="97"/>
       <c r="G7" s="98"/>
       <c r="I7" s="66" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="L7">
         <v>13</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -71565,22 +74093,22 @@
     </row>
     <row r="8" spans="1:15" ht="26.25">
       <c r="A8" s="66" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="E8" s="96"/>
       <c r="F8" s="97"/>
       <c r="G8" s="98"/>
       <c r="I8" s="66" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -71588,22 +74116,22 @@
     </row>
     <row r="9" spans="1:15" ht="26.25">
       <c r="A9" s="66" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="E9" s="96"/>
       <c r="F9" s="97"/>
       <c r="G9" s="98"/>
       <c r="I9" s="66" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="L9">
         <v>3</v>
       </c>
       <c r="N9" s="29" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -71611,22 +74139,22 @@
     </row>
     <row r="10" spans="1:15" ht="26.25">
       <c r="A10" s="66" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="E10" s="96"/>
       <c r="F10" s="97"/>
       <c r="G10" s="98"/>
       <c r="I10" s="66" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>754</v>
+        <v>810</v>
       </c>
       <c r="L10">
         <v>2</v>
       </c>
       <c r="N10" s="29" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="O10">
         <v>4</v>
@@ -71634,16 +74162,16 @@
     </row>
     <row r="11" spans="1:15" ht="26.25">
       <c r="A11" s="66" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="E11" s="96"/>
       <c r="F11" s="97"/>
       <c r="G11" s="98"/>
       <c r="I11" s="66" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="K11" s="29" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="L11">
         <v>4</v>
@@ -71657,22 +74185,22 @@
     </row>
     <row r="12" spans="1:15" ht="26.25">
       <c r="A12" s="66" t="s">
-        <v>754</v>
+        <v>810</v>
       </c>
       <c r="E12" s="96"/>
       <c r="F12" s="97"/>
       <c r="G12" s="98"/>
       <c r="I12" s="66" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="L12">
         <v>10</v>
       </c>
       <c r="N12" s="29" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="O12">
         <v>3</v>
@@ -71680,13 +74208,13 @@
     </row>
     <row r="13" spans="1:15" ht="26.25">
       <c r="A13" s="67" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="E13" s="96"/>
       <c r="F13" s="97"/>
       <c r="G13" s="98"/>
       <c r="I13" s="66" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="K13" s="29" t="s">
         <v>18</v>
@@ -71695,7 +74223,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="29" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="O13">
         <v>3</v>
@@ -71703,22 +74231,22 @@
     </row>
     <row r="14" spans="1:15" ht="26.25">
       <c r="A14" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="E14" s="96"/>
       <c r="F14" s="97"/>
       <c r="G14" s="98"/>
       <c r="I14" s="66" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>756</v>
+        <v>812</v>
       </c>
       <c r="L14">
         <v>1</v>
       </c>
       <c r="N14" s="29" t="s">
-        <v>754</v>
+        <v>810</v>
       </c>
       <c r="O14">
         <v>2</v>
@@ -71726,22 +74254,22 @@
     </row>
     <row r="15" spans="1:15" ht="26.25">
       <c r="A15" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="E15" s="96"/>
       <c r="F15" s="97"/>
       <c r="G15" s="98"/>
       <c r="I15" s="66" t="s">
-        <v>754</v>
+        <v>810</v>
       </c>
       <c r="K15" s="29" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
       <c r="L15">
         <v>1</v>
       </c>
       <c r="N15" s="29" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="O15">
         <v>2</v>
@@ -71749,13 +74277,13 @@
     </row>
     <row r="16" spans="1:15" ht="26.25">
       <c r="A16" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="E16" s="96"/>
       <c r="F16" s="97"/>
       <c r="G16" s="98"/>
       <c r="I16" s="67" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="K16" s="29" t="s">
         <v>9</v>
@@ -71764,7 +74292,7 @@
         <v>4</v>
       </c>
       <c r="N16" s="29" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -71772,16 +74300,16 @@
     </row>
     <row r="17" spans="1:15" ht="26.25">
       <c r="A17" s="67" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="E17" s="96"/>
       <c r="F17" s="97"/>
       <c r="G17" s="98"/>
       <c r="I17" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="K17" s="29" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="L17">
         <v>3</v>
@@ -71795,22 +74323,22 @@
     </row>
     <row r="18" spans="1:15" ht="26.25">
       <c r="A18" s="67" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="E18" s="96"/>
       <c r="F18" s="97"/>
       <c r="G18" s="98"/>
       <c r="I18" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="N18" s="29" t="s">
-        <v>756</v>
+        <v>812</v>
       </c>
       <c r="O18">
         <v>1</v>
@@ -71818,22 +74346,22 @@
     </row>
     <row r="19" spans="1:15" ht="26.25">
       <c r="A19" s="67" t="s">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="E19" s="96"/>
       <c r="F19" s="97"/>
       <c r="G19" s="98"/>
       <c r="I19" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="L19">
         <v>1</v>
       </c>
       <c r="N19" s="29" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
       <c r="O19">
         <v>1</v>
@@ -71841,22 +74369,22 @@
     </row>
     <row r="20" spans="1:15" ht="26.25">
       <c r="A20" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="E20" s="99"/>
       <c r="F20" s="100"/>
       <c r="G20" s="101"/>
       <c r="I20" s="67" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="L20">
         <v>1</v>
       </c>
       <c r="N20" s="29" t="s">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="O20">
         <v>1</v>
@@ -71864,19 +74392,19 @@
     </row>
     <row r="21" spans="1:15" ht="26.25">
       <c r="A21" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I21" s="67" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="K21" s="29" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="L21">
         <v>2</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="O21">
         <v>1</v>
@@ -71884,10 +74412,10 @@
     </row>
     <row r="22" spans="1:15" ht="26.25">
       <c r="A22" s="67" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="I22" s="67" t="s">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="K22" s="29" t="s">
         <v>27</v>
@@ -71900,26 +74428,26 @@
     </row>
     <row r="23" spans="1:15" ht="26.25">
       <c r="A23" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I23" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="26.25">
       <c r="A24" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I24" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="26.25">
       <c r="A25" s="67" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="I25" s="67" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="26.25">
@@ -71927,36 +74455,36 @@
         <v>18</v>
       </c>
       <c r="I26" s="67" t="s">
-        <v>754</v>
+        <v>810</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="26.25">
       <c r="A27" s="67" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
       <c r="I27" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="26.25">
       <c r="A28" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I28" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="26.25">
       <c r="A29" s="67" t="s">
-        <v>756</v>
+        <v>812</v>
       </c>
       <c r="I29" s="67" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="26.25">
       <c r="A30" s="67" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="I30" s="67" t="s">
         <v>18</v>
@@ -71964,50 +74492,50 @@
     </row>
     <row r="31" spans="1:15" ht="26.25">
       <c r="A31" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I31" s="67" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="26.25">
       <c r="A32" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I32" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="26.25">
       <c r="A33" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I33" s="67" t="s">
-        <v>756</v>
+        <v>812</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="26.25">
       <c r="A34" s="67" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="I34" s="67" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="26.25">
       <c r="A35" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I35" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="26.25">
       <c r="A36" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I36" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="26.25">
@@ -72015,28 +74543,28 @@
         <v>9</v>
       </c>
       <c r="I37" s="67" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="26.25">
       <c r="A38" s="67" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="I38" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="26.25">
       <c r="A39" s="68" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="I39" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="25.5">
       <c r="A40" s="69" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="I40" s="67" t="s">
         <v>9</v>
@@ -72044,18 +74572,18 @@
     </row>
     <row r="41" spans="1:9" ht="26.25">
       <c r="A41" s="67" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
       <c r="I41" s="67" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="26.25">
       <c r="A42" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I42" s="68" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="26.25">
@@ -72063,7 +74591,7 @@
         <v>9</v>
       </c>
       <c r="I43" s="67" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="25.5">
@@ -72071,15 +74599,15 @@
         <v>9</v>
       </c>
       <c r="I44" s="69" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="26.25">
       <c r="A45" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I45" s="67" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="26.25">
@@ -72087,12 +74615,12 @@
         <v>9</v>
       </c>
       <c r="I46" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="26.25">
       <c r="A47" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I47" s="67" t="s">
         <v>9</v>
@@ -72100,7 +74628,7 @@
     </row>
     <row r="48" spans="1:9" ht="26.25">
       <c r="A48" s="67" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="I48" s="67" t="s">
         <v>9</v>
@@ -72108,15 +74636,15 @@
     </row>
     <row r="49" spans="1:9" ht="26.25">
       <c r="A49" s="67" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="I49" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="26.25">
       <c r="A50" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I50" s="67" t="s">
         <v>9</v>
@@ -72124,70 +74652,70 @@
     </row>
     <row r="51" spans="1:9" ht="26.25">
       <c r="A51" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I51" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="26.25">
       <c r="A52" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I52" s="67" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="26.25">
       <c r="A53" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I53" s="67" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="26.25">
       <c r="A54" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="I54" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="26.25">
       <c r="A55" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I55" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="26.25">
       <c r="A56" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="I56" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="26.25">
       <c r="I57" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="26.25">
       <c r="I58" s="67" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="26.25">
       <c r="I59" s="67" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="26.25">
       <c r="I60" s="67" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -72201,13 +74729,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A1FB1E-1FF8-4B23-9658-F660DF1E5269}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46.5703125" style="27" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="12" max="12" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -72222,16 +74752,16 @@
     <row r="2" spans="1:20" ht="15.75" thickBot="1"/>
     <row r="3" spans="1:20">
       <c r="A3" s="28" t="s">
-        <v>759</v>
+        <v>815</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>698</v>
+        <v>754</v>
       </c>
       <c r="S3" s="92" t="s">
         <v>28</v>
       </c>
       <c r="T3" s="92" t="s">
-        <v>759</v>
+        <v>815</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -72239,7 +74769,7 @@
         <v>53</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
@@ -72248,7 +74778,7 @@
         <v>2.4</v>
       </c>
       <c r="S4" s="29" t="s">
-        <v>760</v>
+        <v>816</v>
       </c>
       <c r="T4">
         <v>66</v>
@@ -72259,7 +74789,7 @@
         <v>2.7</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="T5">
         <v>41</v>
@@ -72273,7 +74803,7 @@
         <v>3</v>
       </c>
       <c r="S6" s="29" t="s">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="T6">
         <v>41</v>
@@ -72316,7 +74846,7 @@
         <v>2.6</v>
       </c>
       <c r="S8" s="29" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="T8">
         <v>38</v>
@@ -72339,7 +74869,7 @@
         <v>2.9</v>
       </c>
       <c r="S9" s="29" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="T9">
         <v>24</v>
@@ -72359,7 +74889,7 @@
         <v>2.9</v>
       </c>
       <c r="S10" s="29" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="T10">
         <v>20</v>
@@ -72379,7 +74909,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="S11" s="29" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="T11">
         <v>20</v>
@@ -72402,7 +74932,7 @@
         <v>3.1</v>
       </c>
       <c r="S12" s="29" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="T12">
         <v>13</v>
@@ -72422,7 +74952,7 @@
         <v>2.9</v>
       </c>
       <c r="S13" s="29" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="T13">
         <v>11</v>
@@ -72468,7 +74998,7 @@
         <v>2.9</v>
       </c>
       <c r="S15" s="29" t="s">
-        <v>756</v>
+        <v>812</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -72488,7 +75018,7 @@
         <v>2.1</v>
       </c>
       <c r="S16" s="29" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -72509,7 +75039,7 @@
       </c>
       <c r="O17" s="17"/>
       <c r="S17" s="29" t="s">
-        <v>762</v>
+        <v>817</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -72532,7 +75062,7 @@
         <v>2.9</v>
       </c>
       <c r="S18" s="29" t="s">
-        <v>763</v>
+        <v>818</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -72540,7 +75070,7 @@
     </row>
     <row r="19" spans="1:20">
       <c r="S19" s="29" t="s">
-        <v>764</v>
+        <v>819</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -72548,7 +75078,7 @@
     </row>
     <row r="20" spans="1:20">
       <c r="S20" s="29" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
       <c r="T20">
         <v>4</v>
@@ -72559,13 +75089,16 @@
         <v>46174</v>
       </c>
       <c r="B21" t="s">
-        <v>765</v>
+        <v>820</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>766</v>
+        <v>821</v>
+      </c>
+      <c r="J21" s="130" t="s">
+        <v>10</v>
       </c>
       <c r="S21" s="29" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="T21">
         <v>4</v>
@@ -72576,13 +75109,22 @@
         <v>46109</v>
       </c>
       <c r="B22" t="s">
-        <v>767</v>
+        <v>822</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>768</v>
+        <v>823</v>
+      </c>
+      <c r="J22" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" t="s">
+        <v>824</v>
       </c>
       <c r="S22" s="29" t="s">
-        <v>769</v>
+        <v>825</v>
       </c>
       <c r="T22">
         <v>4</v>
@@ -72593,10 +75135,19 @@
         <v>46079</v>
       </c>
       <c r="B23" t="s">
-        <v>770</v>
+        <v>826</v>
+      </c>
+      <c r="J23" s="130" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="M23">
+        <v>8</v>
       </c>
       <c r="S23" s="29" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
       <c r="T23">
         <v>4</v>
@@ -72607,10 +75158,19 @@
         <v>46097</v>
       </c>
       <c r="B24" t="s">
-        <v>771</v>
+        <v>827</v>
+      </c>
+      <c r="J24" s="130" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24">
+        <v>15</v>
       </c>
       <c r="S24" s="29" t="s">
-        <v>772</v>
+        <v>828</v>
       </c>
       <c r="T24">
         <v>4</v>
@@ -72621,125 +75181,848 @@
         <v>231</v>
       </c>
       <c r="B25" t="s">
-        <v>773</v>
+        <v>829</v>
+      </c>
+      <c r="J25" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
       </c>
       <c r="S25" s="29" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="T25">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:20">
+      <c r="J26" s="130" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26">
+        <v>5</v>
+      </c>
       <c r="S26" s="29" t="s">
-        <v>754</v>
+        <v>810</v>
       </c>
       <c r="T26">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:20">
+      <c r="J27" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27">
+        <v>6</v>
+      </c>
       <c r="S27" s="29" t="s">
-        <v>774</v>
+        <v>830</v>
       </c>
       <c r="T27">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:20">
+      <c r="J28" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M28">
+        <v>5</v>
+      </c>
       <c r="S28" s="29" t="s">
-        <v>775</v>
+        <v>831</v>
       </c>
       <c r="T28">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:20">
+      <c r="J29" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="L29" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="M29">
+        <v>10</v>
+      </c>
       <c r="S29" s="29" t="s">
-        <v>776</v>
+        <v>832</v>
       </c>
       <c r="T29">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:20">
+      <c r="J30" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="M30">
+        <v>28</v>
+      </c>
       <c r="S30" s="29" t="s">
-        <v>777</v>
+        <v>833</v>
       </c>
       <c r="T30">
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:20">
+      <c r="J31" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M31">
+        <v>24</v>
+      </c>
       <c r="S31" s="29" t="s">
-        <v>778</v>
+        <v>834</v>
       </c>
       <c r="T31">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:20">
+      <c r="J32" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
       <c r="S32" s="29" t="s">
-        <v>779</v>
+        <v>835</v>
       </c>
       <c r="T32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="19:20">
+    <row r="33" spans="10:20">
+      <c r="J33" s="130" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33">
+        <v>4</v>
+      </c>
       <c r="S33" s="29" t="s">
-        <v>780</v>
+        <v>836</v>
       </c>
       <c r="T33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="19:20">
+    <row r="34" spans="10:20">
+      <c r="J34" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
       <c r="S34" s="29" t="s">
-        <v>781</v>
+        <v>837</v>
       </c>
       <c r="T34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="19:20">
+    <row r="35" spans="10:20">
+      <c r="J35" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35">
+        <v>2</v>
+      </c>
       <c r="S35" s="29" t="s">
-        <v>782</v>
+        <v>838</v>
       </c>
       <c r="T35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="19:20">
+    <row r="36" spans="10:20">
+      <c r="J36" s="130" t="s">
+        <v>10</v>
+      </c>
+      <c r="L36" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M36">
+        <v>15</v>
+      </c>
       <c r="S36" s="29" t="s">
-        <v>783</v>
+        <v>839</v>
       </c>
       <c r="T36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="19:20">
+    <row r="37" spans="10:20">
+      <c r="J37" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37">
+        <v>138</v>
+      </c>
       <c r="S37" s="29" t="s">
-        <v>784</v>
+        <v>840</v>
       </c>
       <c r="T37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="19:20">
+    <row r="38" spans="10:20">
+      <c r="J38" s="130" t="s">
+        <v>22</v>
+      </c>
       <c r="S38" s="29" t="s">
-        <v>785</v>
+        <v>841</v>
       </c>
       <c r="T38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="19:20">
+    <row r="39" spans="10:20">
+      <c r="J39" s="130" t="s">
+        <v>9</v>
+      </c>
       <c r="S39" s="29" t="s">
-        <v>786</v>
+        <v>842</v>
       </c>
       <c r="T39">
         <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="10:20">
+      <c r="J40" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="10:20">
+      <c r="J41" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="10:20">
+      <c r="J42" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="10:20">
+      <c r="J43" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="10:20">
+      <c r="J44" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="10:20">
+      <c r="J45" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="10:20">
+      <c r="J46" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="10:20">
+      <c r="J47" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="10:20">
+      <c r="J48" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="10:10">
+      <c r="J49" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="10:10">
+      <c r="J50" s="130" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="10:10">
+      <c r="J51" s="130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="10:10">
+      <c r="J52" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="10:10">
+      <c r="J53" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="10:10">
+      <c r="J54" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="10:10">
+      <c r="J55" s="130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="10:10">
+      <c r="J56" s="130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="10:10">
+      <c r="J57" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="10:10">
+      <c r="J58" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="10:10">
+      <c r="J59" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="10:10">
+      <c r="J60" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="10:10">
+      <c r="J61" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="10:10">
+      <c r="J62" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="10:10">
+      <c r="J63" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="10:10">
+      <c r="J64" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="10:10">
+      <c r="J65" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="10:10">
+      <c r="J66" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="10:10">
+      <c r="J67" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="10:10">
+      <c r="J68" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="10:10">
+      <c r="J69" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="10:10">
+      <c r="J70" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="10:10">
+      <c r="J71" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="10:10">
+      <c r="J72" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="10:10">
+      <c r="J73" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="10:10">
+      <c r="J74" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="10:10">
+      <c r="J75" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="10:10">
+      <c r="J76" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="10:10">
+      <c r="J77" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="10:10">
+      <c r="J78" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="10:10">
+      <c r="J79" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="10:10">
+      <c r="J80" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="10:10">
+      <c r="J81" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="10:10">
+      <c r="J82" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="10:10">
+      <c r="J83" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="10:10">
+      <c r="J84" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="10:10">
+      <c r="J85" s="130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="10:10">
+      <c r="J86" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="10:10">
+      <c r="J87" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="10:10">
+      <c r="J88" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="10:10">
+      <c r="J89" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="10:10">
+      <c r="J90" s="130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="10:10">
+      <c r="J91" s="130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="10:10">
+      <c r="J92" s="130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="10:10">
+      <c r="J93" s="130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="10:10">
+      <c r="J94" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="10:10">
+      <c r="J95" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="10:10">
+      <c r="J96" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="10:10">
+      <c r="J97" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="10:10">
+      <c r="J98" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="10:10">
+      <c r="J99" s="130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="10:10">
+      <c r="J100" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="10:10">
+      <c r="J101" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="10:10">
+      <c r="J102" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="10:10">
+      <c r="J103" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="10:10">
+      <c r="J104" s="130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="10:10">
+      <c r="J105" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="10:10">
+      <c r="J106" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="10:10">
+      <c r="J107" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="10:10">
+      <c r="J108" s="130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="10:10">
+      <c r="J109" s="130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="10:10">
+      <c r="J110" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="10:10">
+      <c r="J111" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="10:10">
+      <c r="J112" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="10:10">
+      <c r="J113" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="10:10">
+      <c r="J114" s="130" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="10:10">
+      <c r="J115" s="130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="10:10">
+      <c r="J116" s="130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="10:10">
+      <c r="J117" s="130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="10:10">
+      <c r="J118" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="10:10">
+      <c r="J119" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="10:10">
+      <c r="J120" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="10:10">
+      <c r="J121" s="130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="10:10">
+      <c r="J122" s="130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="10:10">
+      <c r="J123" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="10:10">
+      <c r="J124" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="10:10">
+      <c r="J125" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="10:10">
+      <c r="J126" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="10:10">
+      <c r="J127" s="130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="10:10">
+      <c r="J128" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="10:10">
+      <c r="J129" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="10:10">
+      <c r="J130" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="10:10">
+      <c r="J131" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="10:10">
+      <c r="J132" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="10:10">
+      <c r="J133" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="10:10">
+      <c r="J134" s="130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="10:10">
+      <c r="J135" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="10:10">
+      <c r="J136" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="10:10">
+      <c r="J137" s="130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="10:10">
+      <c r="J138" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="10:10">
+      <c r="J139" s="130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="140" spans="10:10">
+      <c r="J140" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="10:10">
+      <c r="J141" s="130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="10:10">
+      <c r="J142" s="130" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="10:10">
+      <c r="J143" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="10:10">
+      <c r="J144" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="10:10">
+      <c r="J145" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="10:10">
+      <c r="J146" s="130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="10:10">
+      <c r="J147" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="10:10">
+      <c r="J148" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="10:10">
+      <c r="J149" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="10:10">
+      <c r="J150" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="10:10">
+      <c r="J151" s="130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="10:10">
+      <c r="J152" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="10:10">
+      <c r="J153" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="10:10">
+      <c r="J154" s="130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="10:10">
+      <c r="J155" s="130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="10:10">
+      <c r="J156" s="130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="10:10">
+      <c r="J157" s="130" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="10:10">
+      <c r="J158" s="143" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="10:10">
+      <c r="J159" s="143" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -72753,6 +76036,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8f6efb83-841f-4bde-8dcd-abbe1dde2f0d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b81dfca8-7f35-4830-97a6-0949ea5d014d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D616D0BEE1F7064CB0A170B949FAEC87" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f7dad44da6bda0413aa3ad92c815d1ff">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b81dfca8-7f35-4830-97a6-0949ea5d014d" xmlns:ns3="8f6efb83-841f-4bde-8dcd-abbe1dde2f0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29141e1502a7a845c866280eabba5962" ns2:_="" ns3:_="">
     <xsd:import namespace="b81dfca8-7f35-4830-97a6-0949ea5d014d"/>
@@ -72965,34 +76268,20 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C89B2C-A7D0-47CB-9EB6-C2EA1D7ECF7C}"/>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8f6efb83-841f-4bde-8dcd-abbe1dde2f0d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b81dfca8-7f35-4830-97a6-0949ea5d014d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB7C508-E84F-4AFE-9A50-BC2770D54856}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50B42307-2CB1-4FDE-B3D1-9FEB02E3C5DC}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C89B2C-A7D0-47CB-9EB6-C2EA1D7ECF7C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB7C508-E84F-4AFE-9A50-BC2770D54856}"/>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a3cceda3-bb16-4686-a971-9fe5d13243fd}" enabled="1" method="Standard" siteId="{4720ed5e-c545-46eb-99a5-958dd333e9f2}" removed="0"/>
+</clbl:labelList>
 </file>